--- a/model/Outputs/11. Interest rate/30/Output Files/0.2/Output_12_42.xlsx
+++ b/model/Outputs/11. Interest rate/30/Output Files/0.2/Output_12_42.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3270846.186402193</v>
+        <v>3271913.958309861</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13633690.08805686</v>
+        <v>13612787.27519204</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13633690.08805686</v>
+        <v>13612787.27519204</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>143186.9484571556</v>
+        <v>135792.8060287174</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>143186.9484571556</v>
+        <v>135792.8060287174</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25064260.45115706</v>
+        <v>25063494.95201828</v>
       </c>
     </row>
   </sheetData>
@@ -669,10 +669,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>3.343301935257443</v>
+        <v>3.34732203575993</v>
       </c>
       <c r="H2" t="n">
-        <v>3.769060713577687</v>
+        <v>3.81023156784903</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -702,16 +702,16 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.953406460791602</v>
+        <v>1.798687867826661</v>
       </c>
       <c r="S2" t="n">
-        <v>85.41253966161941</v>
+        <v>85.50414770182039</v>
       </c>
       <c r="T2" t="n">
-        <v>184.8629887637397</v>
+        <v>184.8805867536895</v>
       </c>
       <c r="U2" t="n">
-        <v>249.1881709204699</v>
+        <v>249.1884925285102</v>
       </c>
       <c r="V2" t="n">
         <v>229.8510241668239</v>
@@ -742,19 +742,19 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H3" t="n">
-        <v>330.0284079411381</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>209.4985557026693</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,19 +778,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>144.7989632036872</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R3" t="n">
-        <v>290.3672935035644</v>
+        <v>133.6519859716245</v>
       </c>
       <c r="S3" t="n">
-        <v>62.44885845517734</v>
+        <v>62.48881128536601</v>
       </c>
       <c r="T3" t="n">
-        <v>4.464774651476091</v>
+        <v>4.473444462796863</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1957842884886531</v>
+        <v>0.1959257979225981</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
@@ -799,10 +799,10 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X3" t="n">
-        <v>19.86273944538755</v>
+        <v>374</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>355.9497235557561</v>
       </c>
     </row>
     <row r="4">
@@ -845,22 +845,22 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>91.51638189435317</v>
+        <v>91.79905402550071</v>
       </c>
       <c r="N4" t="n">
-        <v>142.7621408454554</v>
+        <v>143.0380916651276</v>
       </c>
       <c r="O4" t="n">
-        <v>214.1923837511461</v>
+        <v>214.4472689970478</v>
       </c>
       <c r="P4" t="n">
-        <v>264.9837661807364</v>
+        <v>265.2018645413922</v>
       </c>
       <c r="Q4" t="n">
-        <v>310.286266425598</v>
+        <v>310.437266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>318.2506853582003</v>
+        <v>318.3317673254134</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -912,7 +912,7 @@
         <v>3.769060713577661</v>
       </c>
       <c r="I5" t="n">
-        <v>1.95340646079149</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>85.41253966161939</v>
+        <v>87.36594612241093</v>
       </c>
       <c r="T5" t="n">
         <v>184.8629887637398</v>
@@ -976,22 +976,22 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>176.0205505061529</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H6" t="n">
-        <v>330.0284079411381</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>209.4985557026693</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>144.7989632036872</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>374</v>
+        <v>133.5184388018133</v>
       </c>
       <c r="S6" t="n">
         <v>62.44885845517734</v>
@@ -1033,7 +1033,7 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>291.4125336353057</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
         <v>19.86273944538755</v>
@@ -1143,10 +1143,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>3.343301935257416</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H8" t="n">
-        <v>3.769060713577661</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1176,16 +1176,16 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.953406460791602</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>85.41253966161939</v>
+        <v>87.36594612241093</v>
       </c>
       <c r="T8" t="n">
-        <v>184.8629887637398</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U8" t="n">
-        <v>249.18817092047</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V8" t="n">
         <v>229.8510241668239</v>
@@ -1213,13 +1213,13 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>209.4985557026693</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1252,25 +1252,25 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>144.7989632036872</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>133.5184388018133</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S9" t="n">
-        <v>209.6898787601898</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T9" t="n">
-        <v>4.46477465147608</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1957842884886345</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V9" t="n">
-        <v>14.51066719152016</v>
+        <v>374</v>
       </c>
       <c r="W9" t="n">
-        <v>32.37314290982852</v>
+        <v>166.120904752892</v>
       </c>
       <c r="X9" t="n">
         <v>19.86273944538755</v>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>91.51638189435316</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N10" t="n">
         <v>142.7621408454554</v>
@@ -1328,7 +1328,7 @@
         <v>214.1923837511461</v>
       </c>
       <c r="P10" t="n">
-        <v>264.9837661807365</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q10" t="n">
         <v>310.286266425598</v>
@@ -1383,7 +1383,7 @@
         <v>81.35033711113681</v>
       </c>
       <c r="H11" t="n">
-        <v>72.59985970855254</v>
+        <v>70.10795863165528</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1416,13 +1416,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>143.1742526550738</v>
+        <v>141.7853537319712</v>
       </c>
       <c r="T11" t="n">
         <v>259.5162852461518</v>
       </c>
       <c r="U11" t="n">
-        <v>328.1087337345403</v>
+        <v>328.1087337345404</v>
       </c>
       <c r="V11" t="n">
         <v>308.8510241668239</v>
@@ -1456,16 +1456,16 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F12" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>324.9867056863481</v>
+        <v>3.986705686348103</v>
       </c>
       <c r="H12" t="n">
-        <v>5.417475575159575</v>
+        <v>3.897332469440016</v>
       </c>
       <c r="I12" t="n">
-        <v>191.2065745705938</v>
+        <v>115.7455657933808</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1489,19 +1489,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>76.98115188293241</v>
       </c>
       <c r="R12" t="n">
-        <v>179.532287858417</v>
+        <v>500.532287858417</v>
       </c>
       <c r="S12" t="n">
-        <v>131.5805093985736</v>
+        <v>452.5805093985736</v>
       </c>
       <c r="T12" t="n">
-        <v>81.32333125524967</v>
+        <v>81.32333125524968</v>
       </c>
       <c r="U12" t="n">
-        <v>79.16083145829995</v>
+        <v>79.16083145829998</v>
       </c>
       <c r="V12" t="n">
         <v>414.5106671915202</v>
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>8.713201928270976</v>
+        <v>8.713201928270962</v>
       </c>
       <c r="M13" t="n">
         <v>100.6963655009106</v>
@@ -1574,7 +1574,7 @@
         <v>377.2234394565609</v>
       </c>
       <c r="S13" t="n">
-        <v>30.37429937498658</v>
+        <v>30.37429937498661</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1617,7 +1617,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>81.35033711113681</v>
+        <v>78.85843603423956</v>
       </c>
       <c r="H14" t="n">
         <v>72.59985970855254</v>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>143.1742526550738</v>
+        <v>141.7853537319711</v>
       </c>
       <c r="T14" t="n">
         <v>259.5162852461518</v>
@@ -1681,25 +1681,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>256.2832743226397</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C15" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D15" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E15" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G15" t="n">
-        <v>3.986705686348098</v>
+        <v>324.9867056863481</v>
       </c>
       <c r="H15" t="n">
-        <v>3.897332469439999</v>
+        <v>196.6240501457526</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1857,7 +1857,7 @@
         <v>81.35033711113681</v>
       </c>
       <c r="H17" t="n">
-        <v>72.59985970855251</v>
+        <v>70.10795863166788</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.388898923102697</v>
+        <v>-7.361903858069638e-13</v>
       </c>
       <c r="S17" t="n">
         <v>141.7853537319712</v>
@@ -1924,22 +1924,22 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D18" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E18" t="n">
         <v>21.67209722191262</v>
       </c>
       <c r="F18" t="n">
-        <v>339.6362423378769</v>
+        <v>211.3629600141899</v>
       </c>
       <c r="G18" t="n">
-        <v>324.9867056863481</v>
+        <v>3.986705686348103</v>
       </c>
       <c r="H18" t="n">
-        <v>3.897332469440016</v>
+        <v>324.89733246944</v>
       </c>
       <c r="I18" t="n">
-        <v>191.2065745705938</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1966,7 +1966,7 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>181.0524309641367</v>
+        <v>179.532287858417</v>
       </c>
       <c r="S18" t="n">
         <v>131.5805093985736</v>
@@ -1978,13 +1978,13 @@
         <v>79.16083145829998</v>
       </c>
       <c r="V18" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W18" t="n">
         <v>111.3731429098285</v>
       </c>
       <c r="X18" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y18" t="n">
         <v>78.39139276613435</v>
@@ -2094,7 +2094,7 @@
         <v>81.35033711113681</v>
       </c>
       <c r="H20" t="n">
-        <v>72.59985970855251</v>
+        <v>70.10795863166878</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.388898923102697</v>
+        <v>-4.422312127327774e-12</v>
       </c>
       <c r="S20" t="n">
         <v>141.7853537319712</v>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>63.55655664632661</v>
+        <v>256.2832743226393</v>
       </c>
       <c r="C21" t="n">
         <v>40.09991244551929</v>
@@ -2212,7 +2212,7 @@
         <v>81.32333125524968</v>
       </c>
       <c r="U21" t="n">
-        <v>271.8875491346131</v>
+        <v>79.16083145829998</v>
       </c>
       <c r="V21" t="n">
         <v>93.51066719152016</v>
@@ -2331,7 +2331,7 @@
         <v>81.35033711113681</v>
       </c>
       <c r="H23" t="n">
-        <v>72.59985970855251</v>
+        <v>70.10795863165528</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>143.1742526550738</v>
+        <v>141.7853537319712</v>
       </c>
       <c r="T23" t="n">
         <v>259.5162852461518</v>
@@ -2437,28 +2437,28 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>76.98115188293241</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>500.532287858417</v>
+        <v>179.532287858417</v>
       </c>
       <c r="S24" t="n">
-        <v>452.5805093985736</v>
+        <v>131.5805093985736</v>
       </c>
       <c r="T24" t="n">
         <v>81.32333125524968</v>
       </c>
       <c r="U24" t="n">
-        <v>400.1608314583</v>
+        <v>271.8875491346129</v>
       </c>
       <c r="V24" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W24" t="n">
-        <v>227.1187087032098</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X24" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y24" t="n">
         <v>78.39139276613435</v>
@@ -2568,10 +2568,10 @@
         <v>81.35033711113681</v>
       </c>
       <c r="H26" t="n">
-        <v>72.59985970855254</v>
+        <v>72.59985970855251</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>5.269698923102768</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2598,16 +2598,16 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>5.269698923102768</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>141.7853537319711</v>
+        <v>141.7853537319712</v>
       </c>
       <c r="T26" t="n">
         <v>259.5162852461518</v>
       </c>
       <c r="U26" t="n">
-        <v>328.1087337345403</v>
+        <v>328.1087337345404</v>
       </c>
       <c r="V26" t="n">
         <v>308.8510241668239</v>
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C27" t="n">
-        <v>40.09991244551929</v>
+        <v>232.8266301218323</v>
       </c>
       <c r="D27" t="n">
         <v>26.93768689770263</v>
@@ -2641,16 +2641,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F27" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G27" t="n">
-        <v>3.986705686348098</v>
+        <v>3.986705686348103</v>
       </c>
       <c r="H27" t="n">
-        <v>3.897332469439999</v>
+        <v>3.897332469440016</v>
       </c>
       <c r="I27" t="n">
-        <v>191.2065745705938</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2677,16 +2677,16 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>500.532287858417</v>
+        <v>179.532287858417</v>
       </c>
       <c r="S27" t="n">
-        <v>133.1006525042932</v>
+        <v>131.5805093985736</v>
       </c>
       <c r="T27" t="n">
-        <v>81.32333125524967</v>
+        <v>81.32333125524968</v>
       </c>
       <c r="U27" t="n">
-        <v>79.16083145829995</v>
+        <v>79.16083145829998</v>
       </c>
       <c r="V27" t="n">
         <v>93.51066719152016</v>
@@ -2695,7 +2695,7 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X27" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y27" t="n">
         <v>78.39139276613435</v>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>8.713201928270976</v>
+        <v>8.713201928270962</v>
       </c>
       <c r="M28" t="n">
         <v>100.6963655009106</v>
@@ -2759,7 +2759,7 @@
         <v>377.2234394565609</v>
       </c>
       <c r="S28" t="n">
-        <v>30.37429937498658</v>
+        <v>30.37429937498661</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>81.35033711113681</v>
       </c>
       <c r="H29" t="n">
-        <v>72.59985970855251</v>
+        <v>72.59985970855254</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2835,16 +2835,16 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>5.269698923102768</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>141.7853537319712</v>
+        <v>147.0550526550739</v>
       </c>
       <c r="T29" t="n">
         <v>259.5162852461518</v>
       </c>
       <c r="U29" t="n">
-        <v>328.1087337345404</v>
+        <v>328.1087337345403</v>
       </c>
       <c r="V29" t="n">
         <v>308.8510241668239</v>
@@ -2866,25 +2866,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C30" t="n">
-        <v>155.8454782389005</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D30" t="n">
-        <v>26.93768689770263</v>
+        <v>219.6644045740157</v>
       </c>
       <c r="E30" t="n">
         <v>21.67209722191262</v>
       </c>
       <c r="F30" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
-        <v>3.986705686348103</v>
+        <v>3.986705686348098</v>
       </c>
       <c r="H30" t="n">
-        <v>3.897332469440016</v>
+        <v>3.897332469439999</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2911,25 +2911,25 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>76.98115188293241</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>500.532287858417</v>
+        <v>179.532287858417</v>
       </c>
       <c r="S30" t="n">
         <v>131.5805093985736</v>
       </c>
       <c r="T30" t="n">
-        <v>81.32333125524968</v>
+        <v>81.32333125524967</v>
       </c>
       <c r="U30" t="n">
-        <v>400.1608314583</v>
+        <v>79.16083145829995</v>
       </c>
       <c r="V30" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W30" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X30" t="n">
         <v>98.86273944538755</v>
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>8.713201928270962</v>
+        <v>8.713201928270976</v>
       </c>
       <c r="M31" t="n">
         <v>100.6963655009106</v>
@@ -2996,7 +2996,7 @@
         <v>377.2234394565609</v>
       </c>
       <c r="S31" t="n">
-        <v>30.37429937498661</v>
+        <v>30.37429937498658</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3042,10 +3042,10 @@
         <v>81.35033711113681</v>
       </c>
       <c r="H32" t="n">
-        <v>72.59985970855254</v>
+        <v>72.59985970855251</v>
       </c>
       <c r="I32" t="n">
-        <v>5.269698923102741</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3072,16 +3072,16 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>5.269698923102768</v>
       </c>
       <c r="S32" t="n">
-        <v>141.7853537319711</v>
+        <v>141.7853537319712</v>
       </c>
       <c r="T32" t="n">
         <v>259.5162852461518</v>
       </c>
       <c r="U32" t="n">
-        <v>328.1087337345403</v>
+        <v>328.1087337345404</v>
       </c>
       <c r="V32" t="n">
         <v>308.8510241668239</v>
@@ -3109,19 +3109,19 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D33" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E33" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F33" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G33" t="n">
-        <v>3.986705686348098</v>
+        <v>3.986705686348103</v>
       </c>
       <c r="H33" t="n">
-        <v>3.897332469439999</v>
+        <v>3.897332469440016</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3151,25 +3151,25 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>179.532287858417</v>
+        <v>500.532287858417</v>
       </c>
       <c r="S33" t="n">
-        <v>131.5805093985736</v>
+        <v>324.3072270748871</v>
       </c>
       <c r="T33" t="n">
-        <v>81.32333125524967</v>
+        <v>81.32333125524968</v>
       </c>
       <c r="U33" t="n">
-        <v>271.8875491346131</v>
+        <v>79.16083145829998</v>
       </c>
       <c r="V33" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W33" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X33" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y33" t="n">
         <v>78.39139276613435</v>
@@ -3212,7 +3212,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>8.713201928270976</v>
+        <v>8.713201928270962</v>
       </c>
       <c r="M34" t="n">
         <v>100.6963655009106</v>
@@ -3233,7 +3233,7 @@
         <v>377.2234394565609</v>
       </c>
       <c r="S34" t="n">
-        <v>30.37429937498658</v>
+        <v>30.37429937498661</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3261,25 +3261,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>136.9993129555745</v>
+        <v>137.9993129555745</v>
       </c>
       <c r="C35" t="n">
-        <v>104.4745782429939</v>
+        <v>105.4745782429939</v>
       </c>
       <c r="D35" t="n">
-        <v>65.33915573984979</v>
+        <v>66.33915573984979</v>
       </c>
       <c r="E35" t="n">
-        <v>59.36328960686865</v>
+        <v>60.36328960686865</v>
       </c>
       <c r="F35" t="n">
-        <v>59.88962870801186</v>
+        <v>60.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>45.46723603423962</v>
+        <v>51.87123603423986</v>
       </c>
       <c r="H35" t="n">
-        <v>48.59985970855254</v>
+        <v>49.59985970855251</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3312,25 +3312,25 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>117.7853537319711</v>
+        <v>118.7853537319712</v>
       </c>
       <c r="T35" t="n">
-        <v>235.5162852461518</v>
+        <v>236.5162852461518</v>
       </c>
       <c r="U35" t="n">
-        <v>304.1087337345403</v>
+        <v>305.1087337345404</v>
       </c>
       <c r="V35" t="n">
-        <v>284.8510241668239</v>
+        <v>285.8510241668239</v>
       </c>
       <c r="W35" t="n">
-        <v>293.3734759809475</v>
+        <v>294.3734759809475</v>
       </c>
       <c r="X35" t="n">
-        <v>247.2818334606677</v>
+        <v>248.2818334606677</v>
       </c>
       <c r="Y35" t="n">
-        <v>166.3174326828064</v>
+        <v>167.3174326828064</v>
       </c>
     </row>
     <row r="36">
@@ -3340,22 +3340,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>39.55655664632661</v>
+        <v>82.61046199949732</v>
       </c>
       <c r="C36" t="n">
-        <v>16.09991244551929</v>
+        <v>17.09991244551929</v>
       </c>
       <c r="D36" t="n">
-        <v>347.9376868977026</v>
+        <v>3.937686897702633</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>324.9867056863481</v>
       </c>
       <c r="H36" t="n">
         <v>324.89733246944</v>
@@ -3388,28 +3388,28 @@
         <v>76.98115188293241</v>
       </c>
       <c r="R36" t="n">
-        <v>175.383605673296</v>
+        <v>500.532287858417</v>
       </c>
       <c r="S36" t="n">
-        <v>107.5805093985736</v>
+        <v>452.5805093985736</v>
       </c>
       <c r="T36" t="n">
-        <v>57.32333125524966</v>
+        <v>58.32333125524968</v>
       </c>
       <c r="U36" t="n">
-        <v>55.16083145829995</v>
+        <v>56.16083145829998</v>
       </c>
       <c r="V36" t="n">
-        <v>69.51066719152016</v>
+        <v>70.51066719152016</v>
       </c>
       <c r="W36" t="n">
-        <v>87.37314290982852</v>
+        <v>88.37314290982852</v>
       </c>
       <c r="X36" t="n">
-        <v>74.86273944538755</v>
+        <v>75.86273944538755</v>
       </c>
       <c r="Y36" t="n">
-        <v>54.39139276613435</v>
+        <v>55.39139276613435</v>
       </c>
     </row>
     <row r="37">
@@ -3452,25 +3452,25 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>76.69636550091056</v>
+        <v>77.69636550091059</v>
       </c>
       <c r="N37" t="n">
-        <v>129.602288386439</v>
+        <v>130.602288386439</v>
       </c>
       <c r="O37" t="n">
-        <v>206.2357280134412</v>
+        <v>207.2357280134412</v>
       </c>
       <c r="P37" t="n">
-        <v>266.1134710987693</v>
+        <v>267.1134710987693</v>
       </c>
       <c r="Q37" t="n">
-        <v>327.989266425598</v>
+        <v>328.989266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>353.2234394565609</v>
+        <v>354.2234394565609</v>
       </c>
       <c r="S37" t="n">
-        <v>6.374299374986586</v>
+        <v>7.374299374986606</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3498,25 +3498,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>136.9993129555745</v>
+        <v>137.9993129555745</v>
       </c>
       <c r="C38" t="n">
-        <v>104.4745782429939</v>
+        <v>105.4745782429939</v>
       </c>
       <c r="D38" t="n">
-        <v>65.33915573984979</v>
+        <v>66.33915573984979</v>
       </c>
       <c r="E38" t="n">
-        <v>59.36328960686865</v>
+        <v>60.36328960686865</v>
       </c>
       <c r="F38" t="n">
-        <v>48.00652763111466</v>
+        <v>54.41052763111532</v>
       </c>
       <c r="G38" t="n">
-        <v>57.35033711113682</v>
+        <v>58.35033711113682</v>
       </c>
       <c r="H38" t="n">
-        <v>48.59985970855254</v>
+        <v>49.59985970855254</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3549,25 +3549,25 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>117.7853537319711</v>
+        <v>118.7853537319711</v>
       </c>
       <c r="T38" t="n">
-        <v>235.5162852461518</v>
+        <v>236.5162852461518</v>
       </c>
       <c r="U38" t="n">
-        <v>304.1087337345403</v>
+        <v>305.1087337345403</v>
       </c>
       <c r="V38" t="n">
-        <v>284.8510241668239</v>
+        <v>285.8510241668239</v>
       </c>
       <c r="W38" t="n">
-        <v>293.3734759809475</v>
+        <v>294.3734759809475</v>
       </c>
       <c r="X38" t="n">
-        <v>247.2818334606677</v>
+        <v>248.2818334606677</v>
       </c>
       <c r="Y38" t="n">
-        <v>166.3174326828064</v>
+        <v>167.3174326828064</v>
       </c>
     </row>
     <row r="39">
@@ -3577,13 +3577,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>39.55655664632661</v>
+        <v>40.55655664632661</v>
       </c>
       <c r="C39" t="n">
-        <v>16.09991244551929</v>
+        <v>17.09991244551929</v>
       </c>
       <c r="D39" t="n">
-        <v>2.937686897702633</v>
+        <v>3.937686897702633</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -3592,10 +3592,10 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>324.9867056863481</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>324.89733246944</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3622,31 +3622,31 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>76.98115188293241</v>
       </c>
       <c r="R39" t="n">
-        <v>155.532287858417</v>
+        <v>500.532287858417</v>
       </c>
       <c r="S39" t="n">
-        <v>107.5805093985736</v>
+        <v>452.5805093985736</v>
       </c>
       <c r="T39" t="n">
-        <v>166.4774348265022</v>
+        <v>402.3233312552497</v>
       </c>
       <c r="U39" t="n">
-        <v>55.16083145829995</v>
+        <v>60.09877496725874</v>
       </c>
       <c r="V39" t="n">
-        <v>414.5106671915202</v>
+        <v>70.51066719152016</v>
       </c>
       <c r="W39" t="n">
-        <v>87.37314290982852</v>
+        <v>88.37314290982852</v>
       </c>
       <c r="X39" t="n">
         <v>419.8627394453875</v>
       </c>
       <c r="Y39" t="n">
-        <v>54.39139276613435</v>
+        <v>55.39139276613435</v>
       </c>
     </row>
     <row r="40">
@@ -3689,25 +3689,25 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>76.69636550091056</v>
+        <v>77.69636550091056</v>
       </c>
       <c r="N40" t="n">
-        <v>129.602288386439</v>
+        <v>130.602288386439</v>
       </c>
       <c r="O40" t="n">
-        <v>206.2357280134412</v>
+        <v>207.2357280134412</v>
       </c>
       <c r="P40" t="n">
-        <v>266.1134710987693</v>
+        <v>267.1134710987693</v>
       </c>
       <c r="Q40" t="n">
-        <v>327.989266425598</v>
+        <v>328.989266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>353.2234394565609</v>
+        <v>354.2234394565609</v>
       </c>
       <c r="S40" t="n">
-        <v>6.374299374986586</v>
+        <v>7.374299374986586</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3738,13 +3738,13 @@
         <v>160.9993129555745</v>
       </c>
       <c r="C41" t="n">
-        <v>107.7704584336479</v>
+        <v>121.1985923006668</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>89.33915573984979</v>
       </c>
       <c r="E41" t="n">
-        <v>83.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -3786,13 +3786,13 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>141.7853537319711</v>
+        <v>141.7853537319712</v>
       </c>
       <c r="T41" t="n">
         <v>259.5162852461518</v>
       </c>
       <c r="U41" t="n">
-        <v>328.1087337345403</v>
+        <v>328.1087337345404</v>
       </c>
       <c r="V41" t="n">
         <v>308.8510241668239</v>
@@ -3814,22 +3814,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C42" t="n">
         <v>40.09991244551929</v>
       </c>
       <c r="D42" t="n">
-        <v>200.7834509091653</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E42" t="n">
         <v>21.67209722191262</v>
       </c>
       <c r="F42" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G42" t="n">
-        <v>3.986705686348098</v>
+        <v>3.986705686348103</v>
       </c>
       <c r="H42" t="n">
         <v>324.89733246944</v>
@@ -3862,25 +3862,25 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>179.532287858417</v>
+        <v>372.25900553473</v>
       </c>
       <c r="S42" t="n">
         <v>131.5805093985736</v>
       </c>
       <c r="T42" t="n">
-        <v>81.32333125524967</v>
+        <v>81.32333125524968</v>
       </c>
       <c r="U42" t="n">
-        <v>79.16083145829995</v>
+        <v>79.16083145829998</v>
       </c>
       <c r="V42" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W42" t="n">
         <v>111.3731429098285</v>
       </c>
       <c r="X42" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y42" t="n">
         <v>78.39139276613435</v>
@@ -3923,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>8.713201928270976</v>
+        <v>8.713201928270962</v>
       </c>
       <c r="M43" t="n">
         <v>100.6963655009106</v>
@@ -3944,7 +3944,7 @@
         <v>377.2234394565609</v>
       </c>
       <c r="S43" t="n">
-        <v>30.37429937498658</v>
+        <v>30.37429937498661</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3975,22 +3975,22 @@
         <v>160.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>128.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>89.33915573984979</v>
+        <v>82.06316979752266</v>
       </c>
       <c r="E44" t="n">
-        <v>5.740120505210458</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>83.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>81.35033711113681</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>72.59985970855251</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>141.7853537319712</v>
       </c>
       <c r="T44" t="n">
         <v>259.5162852461518</v>
@@ -4054,16 +4054,16 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C45" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D45" t="n">
         <v>26.93768689770263</v>
       </c>
       <c r="E45" t="n">
-        <v>21.67209722191262</v>
+        <v>214.3988148982258</v>
       </c>
       <c r="F45" t="n">
-        <v>322.2754317790198</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G45" t="n">
         <v>3.986705686348103</v>
@@ -4072,7 +4072,7 @@
         <v>3.897332469440016</v>
       </c>
       <c r="I45" t="n">
-        <v>191.2065745705938</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4099,10 +4099,10 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>500.532287858417</v>
+        <v>179.532287858417</v>
       </c>
       <c r="S45" t="n">
-        <v>452.5805093985736</v>
+        <v>131.5805093985736</v>
       </c>
       <c r="T45" t="n">
         <v>81.32333125524968</v>
@@ -4114,7 +4114,7 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W45" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X45" t="n">
         <v>98.86273944538755</v>
@@ -4297,22 +4297,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>106.8684999460195</v>
+        <v>106.914147375084</v>
       </c>
       <c r="C2" t="n">
-        <v>56.89417848844992</v>
+        <v>56.9398259175144</v>
       </c>
       <c r="D2" t="n">
-        <v>46.450586832036</v>
+        <v>46.49623426110047</v>
       </c>
       <c r="E2" t="n">
-        <v>42.04322359277474</v>
+        <v>42.08887102183921</v>
       </c>
       <c r="F2" t="n">
-        <v>37.10420469579307</v>
+        <v>37.14985212485754</v>
       </c>
       <c r="G2" t="n">
-        <v>33.72713203391686</v>
+        <v>33.76871875540306</v>
       </c>
       <c r="H2" t="n">
         <v>29.92</v>
@@ -4321,52 +4321,52 @@
         <v>29.92</v>
       </c>
       <c r="J2" t="n">
-        <v>400.18</v>
+        <v>29.92</v>
       </c>
       <c r="K2" t="n">
-        <v>452.3245884924623</v>
+        <v>81.5583303517588</v>
       </c>
       <c r="L2" t="n">
-        <v>517.0145614572864</v>
+        <v>145.6202453266332</v>
       </c>
       <c r="M2" t="n">
-        <v>517.0145614572864</v>
+        <v>327.128108133742</v>
       </c>
       <c r="N2" t="n">
-        <v>517.0145614572864</v>
+        <v>697.388108133742</v>
       </c>
       <c r="O2" t="n">
-        <v>887.2745614572864</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="P2" t="n">
-        <v>1257.534561457286</v>
+        <v>1125.74</v>
       </c>
       <c r="Q2" t="n">
         <v>1496</v>
       </c>
       <c r="R2" t="n">
-        <v>1494.026862160817</v>
+        <v>1494.183143567852</v>
       </c>
       <c r="S2" t="n">
-        <v>1407.751569573322</v>
+        <v>1407.815317606417</v>
       </c>
       <c r="T2" t="n">
-        <v>1221.021277892777</v>
+        <v>1221.067250178448</v>
       </c>
       <c r="U2" t="n">
-        <v>969.3160547407873</v>
+        <v>969.3617021698518</v>
       </c>
       <c r="V2" t="n">
-        <v>737.1433030571268</v>
+        <v>737.1889504861913</v>
       </c>
       <c r="W2" t="n">
-        <v>496.3620141874828</v>
+        <v>496.4076616165473</v>
       </c>
       <c r="X2" t="n">
-        <v>302.1379399847881</v>
+        <v>302.1835874138526</v>
       </c>
       <c r="Y2" t="n">
-        <v>189.6960887900342</v>
+        <v>189.7417362190987</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>921.230077122091</v>
+        <v>361.9421914987495</v>
       </c>
       <c r="C3" t="n">
-        <v>921.230077122091</v>
+        <v>361.9421914987495</v>
       </c>
       <c r="D3" t="n">
-        <v>921.230077122091</v>
+        <v>361.9421914987495</v>
       </c>
       <c r="E3" t="n">
-        <v>575.0966455848054</v>
+        <v>361.9421914987495</v>
       </c>
       <c r="F3" t="n">
-        <v>575.0966455848054</v>
+        <v>361.9421914987495</v>
       </c>
       <c r="G3" t="n">
-        <v>575.0966455848054</v>
+        <v>33.13396963146437</v>
       </c>
       <c r="H3" t="n">
-        <v>241.7346173614335</v>
+        <v>33.13396963146437</v>
       </c>
       <c r="I3" t="n">
-        <v>30.1199146314645</v>
+        <v>33.13396963146437</v>
       </c>
       <c r="J3" t="n">
-        <v>174.7984703728012</v>
+        <v>177.6113405614803</v>
       </c>
       <c r="K3" t="n">
-        <v>399.4085458068072</v>
+        <v>401.8775591086939</v>
       </c>
       <c r="L3" t="n">
-        <v>718.3818833454036</v>
+        <v>720.3885386284223</v>
       </c>
       <c r="M3" t="n">
-        <v>860.0360750882628</v>
+        <v>861.5031803712816</v>
       </c>
       <c r="N3" t="n">
-        <v>1050.360878846775</v>
+        <v>1051.274153846774</v>
       </c>
       <c r="O3" t="n">
-        <v>1341.587921002191</v>
+        <v>1341.994549492757</v>
       </c>
       <c r="P3" t="n">
         <v>1496</v>
       </c>
       <c r="Q3" t="n">
-        <v>1349.738421006376</v>
+        <v>1349.46108157432</v>
       </c>
       <c r="R3" t="n">
-        <v>1056.43812453813</v>
+        <v>1214.459075542376</v>
       </c>
       <c r="S3" t="n">
-        <v>993.3584695329</v>
+        <v>1151.339064143017</v>
       </c>
       <c r="T3" t="n">
-        <v>988.8485961475707</v>
+        <v>1146.820433372515</v>
       </c>
       <c r="U3" t="n">
-        <v>988.6508342400064</v>
+        <v>1146.622528526128</v>
       </c>
       <c r="V3" t="n">
-        <v>973.9935946526123</v>
+        <v>1131.965288938734</v>
       </c>
       <c r="W3" t="n">
-        <v>941.2934502992501</v>
+        <v>1099.265144585372</v>
       </c>
       <c r="X3" t="n">
-        <v>921.230077122091</v>
+        <v>721.4873668075941</v>
       </c>
       <c r="Y3" t="n">
-        <v>921.230077122091</v>
+        <v>361.9421914987495</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>403.2410332809005</v>
+        <v>876.4708337745928</v>
       </c>
       <c r="C4" t="n">
-        <v>529.2430390993362</v>
+        <v>876.4708337745928</v>
       </c>
       <c r="D4" t="n">
-        <v>642.5621832243363</v>
+        <v>876.4708337745928</v>
       </c>
       <c r="E4" t="n">
-        <v>760.3910874357493</v>
+        <v>876.4708337745928</v>
       </c>
       <c r="F4" t="n">
-        <v>812.8674587037166</v>
+        <v>876.4708337745928</v>
       </c>
       <c r="G4" t="n">
-        <v>966.4579049184707</v>
+        <v>876.4708337745928</v>
       </c>
       <c r="H4" t="n">
-        <v>1137.609353356557</v>
+        <v>876.4708337745928</v>
       </c>
       <c r="I4" t="n">
-        <v>1364.272015243459</v>
+        <v>881.2025562401257</v>
       </c>
       <c r="J4" t="n">
-        <v>1364.272015243459</v>
+        <v>1251.462556240126</v>
       </c>
       <c r="K4" t="n">
-        <v>1496</v>
+        <v>1382.983127881912</v>
       </c>
       <c r="L4" t="n">
-        <v>1496</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="M4" t="n">
-        <v>1403.559210207724</v>
+        <v>1294.017231267251</v>
       </c>
       <c r="N4" t="n">
-        <v>1259.355027535547</v>
+        <v>1149.534310393385</v>
       </c>
       <c r="O4" t="n">
-        <v>1042.999084352571</v>
+        <v>932.9209073660642</v>
       </c>
       <c r="P4" t="n">
-        <v>775.3387144730393</v>
+        <v>665.0402361121327</v>
       </c>
       <c r="Q4" t="n">
-        <v>461.9182433360716</v>
+        <v>351.4672397226398</v>
       </c>
       <c r="R4" t="n">
-        <v>140.4529045904148</v>
+        <v>29.92</v>
       </c>
       <c r="S4" t="n">
-        <v>140.4529045904148</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="T4" t="n">
-        <v>140.4529045904148</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="U4" t="n">
-        <v>140.4529045904148</v>
+        <v>505.7585226289696</v>
       </c>
       <c r="V4" t="n">
-        <v>140.4529045904148</v>
+        <v>704.5799155149155</v>
       </c>
       <c r="W4" t="n">
-        <v>140.4529045904148</v>
+        <v>876.4708337745928</v>
       </c>
       <c r="X4" t="n">
-        <v>291.4836956146083</v>
+        <v>876.4708337745928</v>
       </c>
       <c r="Y4" t="n">
-        <v>291.4836956146083</v>
+        <v>876.4708337745928</v>
       </c>
     </row>
     <row r="5">
@@ -4534,49 +4534,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>108.8416377852028</v>
+        <v>106.8684999460195</v>
       </c>
       <c r="C5" t="n">
-        <v>58.86731632763319</v>
+        <v>56.89417848844987</v>
       </c>
       <c r="D5" t="n">
-        <v>48.42372467121926</v>
+        <v>46.45058683203594</v>
       </c>
       <c r="E5" t="n">
-        <v>44.016361431958</v>
+        <v>42.04322359277468</v>
       </c>
       <c r="F5" t="n">
-        <v>39.07734253497633</v>
+        <v>37.10420469579301</v>
       </c>
       <c r="G5" t="n">
-        <v>35.70026987310015</v>
+        <v>33.72713203391683</v>
       </c>
       <c r="H5" t="n">
-        <v>31.89313783918332</v>
+        <v>29.92</v>
       </c>
       <c r="I5" t="n">
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>274.4112051186665</v>
+        <v>400.18</v>
       </c>
       <c r="K5" t="n">
-        <v>326.5557936111288</v>
+        <v>452.3245884924623</v>
       </c>
       <c r="L5" t="n">
-        <v>696.8157936111288</v>
+        <v>517.0145614572864</v>
       </c>
       <c r="M5" t="n">
-        <v>1067.075793611129</v>
+        <v>517.0145614572864</v>
       </c>
       <c r="N5" t="n">
-        <v>1437.335793611129</v>
+        <v>517.0145614572864</v>
       </c>
       <c r="O5" t="n">
-        <v>1437.335793611129</v>
+        <v>755.48</v>
       </c>
       <c r="P5" t="n">
-        <v>1496</v>
+        <v>1125.74</v>
       </c>
       <c r="Q5" t="n">
         <v>1496</v>
@@ -4585,25 +4585,25 @@
         <v>1496</v>
       </c>
       <c r="S5" t="n">
-        <v>1409.724707412506</v>
+        <v>1407.751569573322</v>
       </c>
       <c r="T5" t="n">
-        <v>1222.994415731961</v>
+        <v>1221.021277892777</v>
       </c>
       <c r="U5" t="n">
-        <v>971.2891925799706</v>
+        <v>969.3160547407873</v>
       </c>
       <c r="V5" t="n">
-        <v>739.1164408963101</v>
+        <v>737.1433030571268</v>
       </c>
       <c r="W5" t="n">
-        <v>498.3351520266661</v>
+        <v>496.3620141874828</v>
       </c>
       <c r="X5" t="n">
-        <v>304.1110778239714</v>
+        <v>302.1379399847881</v>
       </c>
       <c r="Y5" t="n">
-        <v>191.6692266292175</v>
+        <v>189.6960887900341</v>
       </c>
     </row>
     <row r="6">
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>574.8967309533409</v>
+        <v>1225.724928051675</v>
       </c>
       <c r="C6" t="n">
-        <v>574.8967309533409</v>
+        <v>1225.724928051675</v>
       </c>
       <c r="D6" t="n">
-        <v>574.8967309533409</v>
+        <v>1047.926392186874</v>
       </c>
       <c r="E6" t="n">
-        <v>574.8967309533409</v>
+        <v>701.7929606495888</v>
       </c>
       <c r="F6" t="n">
-        <v>574.8967309533409</v>
+        <v>358.7260491971879</v>
       </c>
       <c r="G6" t="n">
-        <v>574.8967309533409</v>
+        <v>29.92</v>
       </c>
       <c r="H6" t="n">
-        <v>241.534702729969</v>
+        <v>29.92</v>
       </c>
       <c r="I6" t="n">
         <v>29.92</v>
@@ -4658,31 +4658,31 @@
         <v>1495.800085368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1349.538506374912</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="R6" t="n">
-        <v>971.7607285971344</v>
+        <v>1360.932975467714</v>
       </c>
       <c r="S6" t="n">
-        <v>908.6810735919048</v>
+        <v>1297.853320462484</v>
       </c>
       <c r="T6" t="n">
-        <v>904.1712002065755</v>
+        <v>1293.343447077155</v>
       </c>
       <c r="U6" t="n">
-        <v>903.9734382990111</v>
+        <v>1293.145685169591</v>
       </c>
       <c r="V6" t="n">
-        <v>889.3161987116171</v>
+        <v>1278.488445582197</v>
       </c>
       <c r="W6" t="n">
-        <v>594.9601041305001</v>
+        <v>1245.788301228834</v>
       </c>
       <c r="X6" t="n">
-        <v>574.8967309533409</v>
+        <v>1225.724928051675</v>
       </c>
       <c r="Y6" t="n">
-        <v>574.8967309533409</v>
+        <v>1225.724928051675</v>
       </c>
     </row>
     <row r="7">
@@ -4692,34 +4692,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>613.8389062556099</v>
+        <v>542.5363563064418</v>
       </c>
       <c r="C7" t="n">
-        <v>739.8409120740457</v>
+        <v>542.5363563064418</v>
       </c>
       <c r="D7" t="n">
-        <v>739.8409120740457</v>
+        <v>580.4798119420246</v>
       </c>
       <c r="E7" t="n">
-        <v>739.8409120740457</v>
+        <v>698.3087161534377</v>
       </c>
       <c r="F7" t="n">
-        <v>739.8409120740457</v>
+        <v>698.3087161534377</v>
       </c>
       <c r="G7" t="n">
-        <v>893.4313582887999</v>
+        <v>851.8991623681918</v>
       </c>
       <c r="H7" t="n">
-        <v>1064.582806726886</v>
+        <v>1023.050610806278</v>
       </c>
       <c r="I7" t="n">
-        <v>1291.245468613788</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="J7" t="n">
-        <v>1385.467095409585</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="K7" t="n">
-        <v>1385.467095409585</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="L7" t="n">
         <v>1385.467095409585</v>
@@ -4743,25 +4743,25 @@
         <v>29.92</v>
       </c>
       <c r="S7" t="n">
-        <v>29.92</v>
+        <v>70.37478771712394</v>
       </c>
       <c r="T7" t="n">
-        <v>218.7813496506081</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="U7" t="n">
-        <v>218.7813496506081</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="V7" t="n">
-        <v>218.7813496506081</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="W7" t="n">
-        <v>390.6722679102855</v>
+        <v>431.1270556274095</v>
       </c>
       <c r="X7" t="n">
-        <v>390.6722679102855</v>
+        <v>431.1270556274095</v>
       </c>
       <c r="Y7" t="n">
-        <v>502.0815685893178</v>
+        <v>542.5363563064418</v>
       </c>
     </row>
     <row r="8">
@@ -4774,19 +4774,19 @@
         <v>106.8684999460195</v>
       </c>
       <c r="C8" t="n">
-        <v>56.89417848844987</v>
+        <v>56.89417848844992</v>
       </c>
       <c r="D8" t="n">
-        <v>46.45058683203594</v>
+        <v>46.450586832036</v>
       </c>
       <c r="E8" t="n">
-        <v>42.04322359277468</v>
+        <v>42.04322359277474</v>
       </c>
       <c r="F8" t="n">
-        <v>37.10420469579301</v>
+        <v>37.10420469579307</v>
       </c>
       <c r="G8" t="n">
-        <v>33.72713203391683</v>
+        <v>33.72713203391686</v>
       </c>
       <c r="H8" t="n">
         <v>29.92</v>
@@ -4795,7 +4795,7 @@
         <v>29.92</v>
       </c>
       <c r="J8" t="n">
-        <v>209.7212321538424</v>
+        <v>30.01969029977264</v>
       </c>
       <c r="K8" t="n">
         <v>261.8658206463047</v>
@@ -4819,7 +4819,7 @@
         <v>1496</v>
       </c>
       <c r="R8" t="n">
-        <v>1494.026862160817</v>
+        <v>1496</v>
       </c>
       <c r="S8" t="n">
         <v>1407.751569573322</v>
@@ -4840,7 +4840,7 @@
         <v>302.1379399847881</v>
       </c>
       <c r="Y8" t="n">
-        <v>189.6960887900341</v>
+        <v>189.6960887900342</v>
       </c>
     </row>
     <row r="9">
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>930.7350457196555</v>
+        <v>727.505640524864</v>
       </c>
       <c r="C9" t="n">
-        <v>930.7350457196555</v>
+        <v>727.505640524864</v>
       </c>
       <c r="D9" t="n">
-        <v>930.7350457196555</v>
+        <v>376.0534315372855</v>
       </c>
       <c r="E9" t="n">
-        <v>584.60161418237</v>
+        <v>29.92</v>
       </c>
       <c r="F9" t="n">
-        <v>241.534702729969</v>
+        <v>29.92</v>
       </c>
       <c r="G9" t="n">
-        <v>241.534702729969</v>
+        <v>29.92</v>
       </c>
       <c r="H9" t="n">
-        <v>241.534702729969</v>
+        <v>29.92</v>
       </c>
       <c r="I9" t="n">
         <v>29.92</v>
@@ -4895,31 +4895,31 @@
         <v>1495.800085368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1349.538506374912</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="R9" t="n">
-        <v>1214.671396474091</v>
+        <v>1360.932975467714</v>
       </c>
       <c r="S9" t="n">
-        <v>1002.863438130465</v>
+        <v>1297.853320462485</v>
       </c>
       <c r="T9" t="n">
-        <v>998.3535647451353</v>
+        <v>1293.343447077155</v>
       </c>
       <c r="U9" t="n">
-        <v>998.1558028375709</v>
+        <v>1293.145685169591</v>
       </c>
       <c r="V9" t="n">
-        <v>983.4985632501769</v>
+        <v>915.3679073918131</v>
       </c>
       <c r="W9" t="n">
-        <v>950.7984188968147</v>
+        <v>747.5690137020232</v>
       </c>
       <c r="X9" t="n">
-        <v>930.7350457196555</v>
+        <v>727.505640524864</v>
       </c>
       <c r="Y9" t="n">
-        <v>930.7350457196555</v>
+        <v>727.505640524864</v>
       </c>
     </row>
     <row r="10">
@@ -4929,31 +4929,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>221.4055787413175</v>
+        <v>348.5256741631937</v>
       </c>
       <c r="C10" t="n">
-        <v>221.4055787413175</v>
+        <v>474.5276799816295</v>
       </c>
       <c r="D10" t="n">
-        <v>221.4055787413175</v>
+        <v>587.8468241066296</v>
       </c>
       <c r="E10" t="n">
-        <v>339.2344829527305</v>
+        <v>705.6757283180426</v>
       </c>
       <c r="F10" t="n">
-        <v>463.595455544666</v>
+        <v>830.0367009099781</v>
       </c>
       <c r="G10" t="n">
-        <v>617.1859017594202</v>
+        <v>983.6271471247322</v>
       </c>
       <c r="H10" t="n">
-        <v>788.3373501975062</v>
+        <v>1154.778595562818</v>
       </c>
       <c r="I10" t="n">
-        <v>1015.000012084409</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="J10" t="n">
-        <v>1249.71327269318</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="K10" t="n">
         <v>1381.441257449721</v>
@@ -4980,25 +4980,25 @@
         <v>29.92</v>
       </c>
       <c r="S10" t="n">
-        <v>70.37478771712394</v>
+        <v>29.92</v>
       </c>
       <c r="T10" t="n">
-        <v>70.37478771712394</v>
+        <v>29.92</v>
       </c>
       <c r="U10" t="n">
-        <v>70.37478771712394</v>
+        <v>29.92</v>
       </c>
       <c r="V10" t="n">
-        <v>70.37478771712394</v>
+        <v>29.92</v>
       </c>
       <c r="W10" t="n">
-        <v>70.37478771712394</v>
+        <v>29.92</v>
       </c>
       <c r="X10" t="n">
-        <v>221.4055787413175</v>
+        <v>180.9507910241935</v>
       </c>
       <c r="Y10" t="n">
-        <v>221.4055787413175</v>
+        <v>236.7683364969016</v>
       </c>
     </row>
     <row r="11">
@@ -5008,76 +5008,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>596.3814637549632</v>
+        <v>593.7843919601175</v>
       </c>
       <c r="C11" t="n">
-        <v>466.6091624994138</v>
+        <v>464.0120907045681</v>
       </c>
       <c r="D11" t="n">
-        <v>376.36759104502</v>
+        <v>373.7705192501743</v>
       </c>
       <c r="E11" t="n">
-        <v>292.162248007779</v>
+        <v>289.5651762129333</v>
       </c>
       <c r="F11" t="n">
-        <v>207.4252493128175</v>
+        <v>204.8281775179718</v>
       </c>
       <c r="G11" t="n">
-        <v>125.2531916248006</v>
+        <v>122.6561198299548</v>
       </c>
       <c r="H11" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I11" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J11" t="n">
-        <v>135.4535720585666</v>
+        <v>561.3752612788618</v>
       </c>
       <c r="K11" t="n">
-        <v>777.9635720585666</v>
+        <v>1202.895261278862</v>
       </c>
       <c r="L11" t="n">
-        <v>997.7838685409787</v>
+        <v>1422.715557761274</v>
       </c>
       <c r="M11" t="n">
-        <v>1640.293868540979</v>
+        <v>1637.796970190582</v>
       </c>
       <c r="N11" t="n">
-        <v>2230.820595394003</v>
+        <v>1637.796970190582</v>
       </c>
       <c r="O11" t="n">
-        <v>2395.974106525702</v>
+        <v>1802.950481322281</v>
       </c>
       <c r="P11" t="n">
-        <v>2596</v>
+        <v>2002.976374796579</v>
       </c>
       <c r="Q11" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="R11" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="S11" t="n">
-        <v>2451.379542772653</v>
+        <v>2448.782470977807</v>
       </c>
       <c r="T11" t="n">
-        <v>2189.241880907853</v>
+        <v>2186.644809113007</v>
       </c>
       <c r="U11" t="n">
-        <v>1857.81891753963</v>
+        <v>1855.221845744784</v>
       </c>
       <c r="V11" t="n">
-        <v>1545.84818605799</v>
+        <v>1543.251114263144</v>
       </c>
       <c r="W11" t="n">
-        <v>1225.268917390366</v>
+        <v>1222.67184559552</v>
       </c>
       <c r="X11" t="n">
-        <v>951.2468633896915</v>
+        <v>948.6497915948457</v>
       </c>
       <c r="Y11" t="n">
-        <v>759.0070323969577</v>
+        <v>756.4099606021121</v>
       </c>
     </row>
     <row r="12">
@@ -5087,76 +5087,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1011.472216904154</v>
+        <v>285.1486291436165</v>
       </c>
       <c r="C12" t="n">
-        <v>970.9672548379733</v>
+        <v>244.6436670774353</v>
       </c>
       <c r="D12" t="n">
-        <v>943.7574700928192</v>
+        <v>217.4338823322812</v>
       </c>
       <c r="E12" t="n">
-        <v>921.866462797958</v>
+        <v>195.5428750374199</v>
       </c>
       <c r="F12" t="n">
-        <v>578.7995513455571</v>
+        <v>176.7183878274433</v>
       </c>
       <c r="G12" t="n">
-        <v>250.5301516623772</v>
+        <v>172.6914123866877</v>
       </c>
       <c r="H12" t="n">
-        <v>245.057954111711</v>
+        <v>168.7547129226068</v>
       </c>
       <c r="I12" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J12" t="n">
-        <v>246.2912041375631</v>
+        <v>246.2112041375631</v>
       </c>
       <c r="K12" t="n">
-        <v>555.8339306093051</v>
+        <v>555.753930609305</v>
       </c>
       <c r="L12" t="n">
-        <v>989.0096988082788</v>
+        <v>988.9296988082788</v>
       </c>
       <c r="M12" t="n">
-        <v>1263.932740551138</v>
+        <v>1263.852740551138</v>
       </c>
       <c r="N12" t="n">
-        <v>1591.05362421531</v>
+        <v>1590.97362421531</v>
       </c>
       <c r="O12" t="n">
-        <v>2007.422354200916</v>
+        <v>2007.342354200916</v>
       </c>
       <c r="P12" t="n">
-        <v>2262.271670368536</v>
+        <v>2262.191670368536</v>
       </c>
       <c r="Q12" t="n">
-        <v>2262.271670368536</v>
+        <v>2184.432931092847</v>
       </c>
       <c r="R12" t="n">
-        <v>2080.925925057003</v>
+        <v>1678.84476153889</v>
       </c>
       <c r="S12" t="n">
-        <v>1948.016319603899</v>
+        <v>1221.692731843361</v>
       </c>
       <c r="T12" t="n">
-        <v>1865.871540558192</v>
+        <v>1139.547952797654</v>
       </c>
       <c r="U12" t="n">
-        <v>1785.911104741727</v>
+        <v>1059.58751698119</v>
       </c>
       <c r="V12" t="n">
-        <v>1367.213461113929</v>
+        <v>640.8898733533913</v>
       </c>
       <c r="W12" t="n">
-        <v>1254.715336962587</v>
+        <v>528.3917492020494</v>
       </c>
       <c r="X12" t="n">
-        <v>1154.853983987448</v>
+        <v>428.5303962269104</v>
       </c>
       <c r="Y12" t="n">
-        <v>1075.670758971151</v>
+        <v>349.3471712106131</v>
       </c>
     </row>
     <row r="13">
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>675.5869414962938</v>
+        <v>675.5069414962938</v>
       </c>
       <c r="C13" t="n">
-        <v>723.3789473147295</v>
+        <v>723.2989473147296</v>
       </c>
       <c r="D13" t="n">
-        <v>758.4880914397296</v>
+        <v>758.4080914397297</v>
       </c>
       <c r="E13" t="n">
-        <v>798.1069956511426</v>
+        <v>798.0269956511427</v>
       </c>
       <c r="F13" t="n">
-        <v>844.257968243078</v>
+        <v>844.1779682430781</v>
       </c>
       <c r="G13" t="n">
-        <v>920.0793701955371</v>
+        <v>919.9993701955372</v>
       </c>
       <c r="H13" t="n">
-        <v>1016.941316010672</v>
+        <v>1016.861316010672</v>
       </c>
       <c r="I13" t="n">
-        <v>1178.654719536919</v>
+        <v>1178.574719536919</v>
       </c>
       <c r="J13" t="n">
-        <v>1505.704370025436</v>
+        <v>1505.624370025436</v>
       </c>
       <c r="K13" t="n">
-        <v>1610.453394126239</v>
+        <v>1610.373394126239</v>
       </c>
       <c r="L13" t="n">
-        <v>1601.652180057278</v>
+        <v>1601.572180057279</v>
       </c>
       <c r="M13" t="n">
-        <v>1499.938679551308</v>
+        <v>1499.858679551308</v>
       </c>
       <c r="N13" t="n">
-        <v>1344.784852898339</v>
+        <v>1344.704852898339</v>
       </c>
       <c r="O13" t="n">
-        <v>1112.223511470621</v>
+        <v>1112.143511470621</v>
       </c>
       <c r="P13" t="n">
-        <v>819.1796012698439</v>
+        <v>819.0996012698439</v>
       </c>
       <c r="Q13" t="n">
-        <v>463.6348877086339</v>
+        <v>463.5548877086338</v>
       </c>
       <c r="R13" t="n">
-        <v>82.60111047978444</v>
+        <v>82.52111047978445</v>
       </c>
       <c r="S13" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="T13" t="n">
-        <v>164.4554332571655</v>
+        <v>164.3754332571655</v>
       </c>
       <c r="U13" t="n">
-        <v>321.7272009811524</v>
+        <v>332.7507078626653</v>
       </c>
       <c r="V13" t="n">
-        <v>442.3385938670984</v>
+        <v>442.2585938670985</v>
       </c>
       <c r="W13" t="n">
-        <v>536.0195121267758</v>
+        <v>535.9395121267759</v>
       </c>
       <c r="X13" t="n">
-        <v>608.8403031509694</v>
+        <v>608.7603031509694</v>
       </c>
       <c r="Y13" t="n">
-        <v>642.0396038300016</v>
+        <v>641.9596038300017</v>
       </c>
     </row>
     <row r="14">
@@ -5245,76 +5245,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>596.3814637549632</v>
+        <v>593.7843919601175</v>
       </c>
       <c r="C14" t="n">
-        <v>466.6091624994138</v>
+        <v>464.0120907045681</v>
       </c>
       <c r="D14" t="n">
-        <v>376.36759104502</v>
+        <v>373.7705192501743</v>
       </c>
       <c r="E14" t="n">
-        <v>292.162248007779</v>
+        <v>289.5651762129333</v>
       </c>
       <c r="F14" t="n">
-        <v>207.4252493128175</v>
+        <v>204.8281775179718</v>
       </c>
       <c r="G14" t="n">
-        <v>125.2531916248006</v>
+        <v>125.1731916248006</v>
       </c>
       <c r="H14" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I14" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J14" t="n">
-        <v>135.4535720585666</v>
+        <v>135.3735720585666</v>
       </c>
       <c r="K14" t="n">
-        <v>312.6439213047977</v>
+        <v>312.5639213047978</v>
       </c>
       <c r="L14" t="n">
-        <v>532.4642177872098</v>
+        <v>532.3842177872099</v>
       </c>
       <c r="M14" t="n">
-        <v>1174.97421778721</v>
+        <v>1173.904217787211</v>
       </c>
       <c r="N14" t="n">
-        <v>1199.31286366488</v>
+        <v>1815.424217787212</v>
       </c>
       <c r="O14" t="n">
-        <v>1364.466374796579</v>
+        <v>1980.577728918911</v>
       </c>
       <c r="P14" t="n">
-        <v>2006.976374796579</v>
+        <v>2180.603622393209</v>
       </c>
       <c r="Q14" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="R14" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="S14" t="n">
-        <v>2451.379542772653</v>
+        <v>2448.782470977807</v>
       </c>
       <c r="T14" t="n">
-        <v>2189.241880907853</v>
+        <v>2186.644809113007</v>
       </c>
       <c r="U14" t="n">
-        <v>1857.81891753963</v>
+        <v>1855.221845744784</v>
       </c>
       <c r="V14" t="n">
-        <v>1545.84818605799</v>
+        <v>1543.251114263144</v>
       </c>
       <c r="W14" t="n">
-        <v>1225.268917390366</v>
+        <v>1222.67184559552</v>
       </c>
       <c r="X14" t="n">
-        <v>951.2468633896915</v>
+        <v>948.6497915948457</v>
       </c>
       <c r="Y14" t="n">
-        <v>759.0070323969577</v>
+        <v>756.4099606021121</v>
       </c>
     </row>
     <row r="15">
@@ -5324,76 +5324,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1141.041188948283</v>
+        <v>1335.634641146578</v>
       </c>
       <c r="C15" t="n">
-        <v>776.2938026396771</v>
+        <v>1295.129679080397</v>
       </c>
       <c r="D15" t="n">
-        <v>424.8415936520986</v>
+        <v>1267.919894335243</v>
       </c>
       <c r="E15" t="n">
-        <v>78.70816211481309</v>
+        <v>921.7864627979573</v>
       </c>
       <c r="F15" t="n">
-        <v>59.88367490483647</v>
+        <v>578.7195513455563</v>
       </c>
       <c r="G15" t="n">
-        <v>55.85669946408081</v>
+        <v>250.4501516623764</v>
       </c>
       <c r="H15" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I15" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J15" t="n">
-        <v>246.2912041375631</v>
+        <v>246.2112041375631</v>
       </c>
       <c r="K15" t="n">
-        <v>555.8339306093051</v>
+        <v>555.753930609305</v>
       </c>
       <c r="L15" t="n">
-        <v>989.0096988082788</v>
+        <v>988.9296988082788</v>
       </c>
       <c r="M15" t="n">
-        <v>1263.932740551138</v>
+        <v>1263.852740551138</v>
       </c>
       <c r="N15" t="n">
-        <v>1591.05362421531</v>
+        <v>1590.97362421531</v>
       </c>
       <c r="O15" t="n">
-        <v>2007.422354200916</v>
+        <v>2007.342354200916</v>
       </c>
       <c r="P15" t="n">
-        <v>2262.271670368536</v>
+        <v>2262.191670368536</v>
       </c>
       <c r="Q15" t="n">
-        <v>2262.271670368536</v>
+        <v>2262.191670368536</v>
       </c>
       <c r="R15" t="n">
-        <v>2080.925925057003</v>
+        <v>2080.845925057003</v>
       </c>
       <c r="S15" t="n">
-        <v>1948.016319603899</v>
+        <v>1947.936319603898</v>
       </c>
       <c r="T15" t="n">
-        <v>1865.871540558192</v>
+        <v>1865.791540558192</v>
       </c>
       <c r="U15" t="n">
-        <v>1785.911104741727</v>
+        <v>1785.831104741727</v>
       </c>
       <c r="V15" t="n">
-        <v>1691.455885356353</v>
+        <v>1691.375885356353</v>
       </c>
       <c r="W15" t="n">
-        <v>1578.957761205011</v>
+        <v>1578.877761205011</v>
       </c>
       <c r="X15" t="n">
-        <v>1479.096408229872</v>
+        <v>1479.016408229872</v>
       </c>
       <c r="Y15" t="n">
-        <v>1399.913183213575</v>
+        <v>1399.833183213575</v>
       </c>
     </row>
     <row r="16">
@@ -5403,76 +5403,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>675.5869414962938</v>
+        <v>686.6104483778066</v>
       </c>
       <c r="C16" t="n">
-        <v>723.3789473147295</v>
+        <v>734.4024541962424</v>
       </c>
       <c r="D16" t="n">
-        <v>758.4880914397296</v>
+        <v>769.5115983212424</v>
       </c>
       <c r="E16" t="n">
-        <v>798.1069956511426</v>
+        <v>809.1305025326554</v>
       </c>
       <c r="F16" t="n">
-        <v>844.257968243078</v>
+        <v>855.2814751245909</v>
       </c>
       <c r="G16" t="n">
-        <v>920.0793701955371</v>
+        <v>931.1028770770499</v>
       </c>
       <c r="H16" t="n">
-        <v>1016.941316010672</v>
+        <v>1027.964822892185</v>
       </c>
       <c r="I16" t="n">
-        <v>1178.654719536919</v>
+        <v>1178.574719536919</v>
       </c>
       <c r="J16" t="n">
-        <v>1505.704370025436</v>
+        <v>1505.624370025436</v>
       </c>
       <c r="K16" t="n">
-        <v>1610.453394126239</v>
+        <v>1610.373394126239</v>
       </c>
       <c r="L16" t="n">
-        <v>1601.652180057278</v>
+        <v>1601.572180057278</v>
       </c>
       <c r="M16" t="n">
-        <v>1499.938679551308</v>
+        <v>1499.858679551308</v>
       </c>
       <c r="N16" t="n">
-        <v>1344.784852898339</v>
+        <v>1344.704852898339</v>
       </c>
       <c r="O16" t="n">
-        <v>1112.223511470621</v>
+        <v>1112.143511470621</v>
       </c>
       <c r="P16" t="n">
-        <v>819.1796012698439</v>
+        <v>819.0996012698439</v>
       </c>
       <c r="Q16" t="n">
-        <v>463.6348877086339</v>
+        <v>463.5548877086338</v>
       </c>
       <c r="R16" t="n">
-        <v>82.60111047978444</v>
+        <v>82.52111047978443</v>
       </c>
       <c r="S16" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="T16" t="n">
-        <v>153.3519263756527</v>
+        <v>164.3754332571655</v>
       </c>
       <c r="U16" t="n">
-        <v>321.7272009811524</v>
+        <v>332.7507078626653</v>
       </c>
       <c r="V16" t="n">
-        <v>442.3385938670984</v>
+        <v>453.3621007486113</v>
       </c>
       <c r="W16" t="n">
-        <v>536.0195121267758</v>
+        <v>547.0430190082886</v>
       </c>
       <c r="X16" t="n">
-        <v>608.8403031509694</v>
+        <v>619.8638100324822</v>
       </c>
       <c r="Y16" t="n">
-        <v>642.0396038300016</v>
+        <v>653.0631107115145</v>
       </c>
     </row>
     <row r="17">
@@ -5482,76 +5482,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>596.3814637549632</v>
+        <v>593.7843919601303</v>
       </c>
       <c r="C17" t="n">
-        <v>466.6091624994138</v>
+        <v>464.0120907045808</v>
       </c>
       <c r="D17" t="n">
-        <v>376.36759104502</v>
+        <v>373.7705192501871</v>
       </c>
       <c r="E17" t="n">
-        <v>292.162248007779</v>
+        <v>289.565176212946</v>
       </c>
       <c r="F17" t="n">
-        <v>207.4252493128175</v>
+        <v>204.8281775179846</v>
       </c>
       <c r="G17" t="n">
-        <v>125.2531916248005</v>
+        <v>122.6561198299676</v>
       </c>
       <c r="H17" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I17" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J17" t="n">
-        <v>135.4535720585666</v>
+        <v>561.3752612788618</v>
       </c>
       <c r="K17" t="n">
-        <v>312.6439213047977</v>
+        <v>738.5656105250929</v>
       </c>
       <c r="L17" t="n">
-        <v>532.4642177872098</v>
+        <v>958.385907007505</v>
       </c>
       <c r="M17" t="n">
-        <v>556.8028636648803</v>
+        <v>1599.905907007506</v>
       </c>
       <c r="N17" t="n">
-        <v>1199.31286366488</v>
+        <v>2226.820595394003</v>
       </c>
       <c r="O17" t="n">
-        <v>1364.466374796579</v>
+        <v>2391.974106525702</v>
       </c>
       <c r="P17" t="n">
-        <v>2006.976374796579</v>
+        <v>2592</v>
       </c>
       <c r="Q17" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="R17" t="n">
-        <v>2594.597071794846</v>
+        <v>2592.000000000012</v>
       </c>
       <c r="S17" t="n">
-        <v>2451.379542772653</v>
+        <v>2448.782470977819</v>
       </c>
       <c r="T17" t="n">
-        <v>2189.241880907853</v>
+        <v>2186.64480911302</v>
       </c>
       <c r="U17" t="n">
-        <v>1857.81891753963</v>
+        <v>1855.221845744797</v>
       </c>
       <c r="V17" t="n">
-        <v>1545.84818605799</v>
+        <v>1543.251114263157</v>
       </c>
       <c r="W17" t="n">
-        <v>1225.268917390366</v>
+        <v>1222.671845595533</v>
       </c>
       <c r="X17" t="n">
-        <v>951.2468633896915</v>
+        <v>948.6497915948585</v>
       </c>
       <c r="Y17" t="n">
-        <v>759.0070323969577</v>
+        <v>756.4099606021248</v>
       </c>
     </row>
     <row r="18">
@@ -5561,76 +5561,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1009.936718817569</v>
+        <v>1011.392216904154</v>
       </c>
       <c r="C18" t="n">
-        <v>969.431756751388</v>
+        <v>970.8872548379729</v>
       </c>
       <c r="D18" t="n">
-        <v>942.2219720062338</v>
+        <v>619.4350458503945</v>
       </c>
       <c r="E18" t="n">
-        <v>920.3309647113726</v>
+        <v>597.5440385555333</v>
       </c>
       <c r="F18" t="n">
-        <v>577.2640532589717</v>
+        <v>384.0460991472607</v>
       </c>
       <c r="G18" t="n">
-        <v>248.9946535757918</v>
+        <v>380.0191237065051</v>
       </c>
       <c r="H18" t="n">
-        <v>245.057954111711</v>
+        <v>51.84</v>
       </c>
       <c r="I18" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J18" t="n">
-        <v>246.2912041375631</v>
+        <v>246.2112041375631</v>
       </c>
       <c r="K18" t="n">
-        <v>555.8339306093051</v>
+        <v>555.753930609305</v>
       </c>
       <c r="L18" t="n">
-        <v>989.0096988082788</v>
+        <v>988.9296988082788</v>
       </c>
       <c r="M18" t="n">
-        <v>1263.932740551138</v>
+        <v>1263.852740551138</v>
       </c>
       <c r="N18" t="n">
-        <v>1591.05362421531</v>
+        <v>1590.97362421531</v>
       </c>
       <c r="O18" t="n">
-        <v>2007.422354200916</v>
+        <v>2007.342354200916</v>
       </c>
       <c r="P18" t="n">
-        <v>2262.271670368536</v>
+        <v>2262.191670368536</v>
       </c>
       <c r="Q18" t="n">
-        <v>2262.271670368536</v>
+        <v>2262.191670368536</v>
       </c>
       <c r="R18" t="n">
-        <v>2079.390426970418</v>
+        <v>2080.845925057003</v>
       </c>
       <c r="S18" t="n">
-        <v>1946.480821517314</v>
+        <v>1947.936319603898</v>
       </c>
       <c r="T18" t="n">
-        <v>1864.336042471607</v>
+        <v>1865.791540558192</v>
       </c>
       <c r="U18" t="n">
-        <v>1784.375606655142</v>
+        <v>1785.831104741727</v>
       </c>
       <c r="V18" t="n">
-        <v>1365.677963027344</v>
+        <v>1691.375885356353</v>
       </c>
       <c r="W18" t="n">
-        <v>1253.179838876002</v>
+        <v>1578.877761205011</v>
       </c>
       <c r="X18" t="n">
-        <v>1153.318485900863</v>
+        <v>1154.773983987448</v>
       </c>
       <c r="Y18" t="n">
-        <v>1074.135260884566</v>
+        <v>1075.590758971151</v>
       </c>
     </row>
     <row r="19">
@@ -5640,76 +5640,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>686.6904483778065</v>
+        <v>675.5069414962938</v>
       </c>
       <c r="C19" t="n">
-        <v>734.4824541962423</v>
+        <v>723.2989473147296</v>
       </c>
       <c r="D19" t="n">
-        <v>769.5915983212424</v>
+        <v>758.4080914397297</v>
       </c>
       <c r="E19" t="n">
-        <v>798.1069956511426</v>
+        <v>798.0269956511427</v>
       </c>
       <c r="F19" t="n">
-        <v>844.257968243078</v>
+        <v>844.1779682430781</v>
       </c>
       <c r="G19" t="n">
-        <v>920.0793701955371</v>
+        <v>919.9993701955372</v>
       </c>
       <c r="H19" t="n">
-        <v>1016.941316010672</v>
+        <v>1016.861316010672</v>
       </c>
       <c r="I19" t="n">
-        <v>1178.654719536919</v>
+        <v>1178.574719536919</v>
       </c>
       <c r="J19" t="n">
-        <v>1505.704370025436</v>
+        <v>1505.624370025436</v>
       </c>
       <c r="K19" t="n">
-        <v>1610.453394126239</v>
+        <v>1610.373394126239</v>
       </c>
       <c r="L19" t="n">
-        <v>1601.652180057278</v>
+        <v>1601.572180057279</v>
       </c>
       <c r="M19" t="n">
-        <v>1499.938679551308</v>
+        <v>1499.858679551308</v>
       </c>
       <c r="N19" t="n">
-        <v>1344.784852898339</v>
+        <v>1344.704852898339</v>
       </c>
       <c r="O19" t="n">
-        <v>1112.223511470621</v>
+        <v>1112.143511470621</v>
       </c>
       <c r="P19" t="n">
-        <v>819.1796012698439</v>
+        <v>819.0996012698439</v>
       </c>
       <c r="Q19" t="n">
-        <v>463.6348877086338</v>
+        <v>463.5548877086338</v>
       </c>
       <c r="R19" t="n">
-        <v>82.60111047978445</v>
+        <v>82.52111047978445</v>
       </c>
       <c r="S19" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="T19" t="n">
-        <v>164.4554332571655</v>
+        <v>153.2719263756527</v>
       </c>
       <c r="U19" t="n">
-        <v>332.8307078626652</v>
+        <v>321.6472009811525</v>
       </c>
       <c r="V19" t="n">
-        <v>453.4421007486112</v>
+        <v>442.2585938670985</v>
       </c>
       <c r="W19" t="n">
-        <v>547.1230190082886</v>
+        <v>535.9395121267759</v>
       </c>
       <c r="X19" t="n">
-        <v>619.9438100324821</v>
+        <v>608.7603031509694</v>
       </c>
       <c r="Y19" t="n">
-        <v>653.1431107115144</v>
+        <v>641.9596038300017</v>
       </c>
     </row>
     <row r="20">
@@ -5719,76 +5719,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>596.3814637549632</v>
+        <v>593.7843919601312</v>
       </c>
       <c r="C20" t="n">
-        <v>466.6091624994138</v>
+        <v>464.0120907045817</v>
       </c>
       <c r="D20" t="n">
-        <v>376.36759104502</v>
+        <v>373.770519250188</v>
       </c>
       <c r="E20" t="n">
-        <v>292.162248007779</v>
+        <v>289.5651762129469</v>
       </c>
       <c r="F20" t="n">
-        <v>207.4252493128175</v>
+        <v>204.8281775179855</v>
       </c>
       <c r="G20" t="n">
-        <v>125.2531916248005</v>
+        <v>122.6561198299685</v>
       </c>
       <c r="H20" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I20" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J20" t="n">
-        <v>135.4535720585666</v>
+        <v>561.3752612788618</v>
       </c>
       <c r="K20" t="n">
-        <v>312.6439213047977</v>
+        <v>738.5656105250929</v>
       </c>
       <c r="L20" t="n">
-        <v>532.4642177872098</v>
+        <v>958.385907007505</v>
       </c>
       <c r="M20" t="n">
-        <v>1174.97421778721</v>
+        <v>1599.905907007506</v>
       </c>
       <c r="N20" t="n">
-        <v>1641.796970190582</v>
+        <v>1637.796970190582</v>
       </c>
       <c r="O20" t="n">
-        <v>1806.950481322281</v>
+        <v>1802.950481322281</v>
       </c>
       <c r="P20" t="n">
-        <v>2006.976374796579</v>
+        <v>2002.976374796579</v>
       </c>
       <c r="Q20" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="R20" t="n">
-        <v>2594.597071794846</v>
+        <v>2592.000000000013</v>
       </c>
       <c r="S20" t="n">
-        <v>2451.379542772653</v>
+        <v>2448.78247097782</v>
       </c>
       <c r="T20" t="n">
-        <v>2189.241880907853</v>
+        <v>2186.644809113021</v>
       </c>
       <c r="U20" t="n">
-        <v>1857.81891753963</v>
+        <v>1855.221845744798</v>
       </c>
       <c r="V20" t="n">
-        <v>1545.84818605799</v>
+        <v>1543.251114263158</v>
       </c>
       <c r="W20" t="n">
-        <v>1225.268917390366</v>
+        <v>1222.671845595534</v>
       </c>
       <c r="X20" t="n">
-        <v>951.2468633896915</v>
+        <v>948.6497915948594</v>
       </c>
       <c r="Y20" t="n">
-        <v>759.0070323969577</v>
+        <v>756.4099606021257</v>
       </c>
     </row>
     <row r="21">
@@ -5798,76 +5798,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1141.041188948283</v>
+        <v>1140.961188948283</v>
       </c>
       <c r="C21" t="n">
-        <v>1100.536226882101</v>
+        <v>1100.456226882101</v>
       </c>
       <c r="D21" t="n">
-        <v>749.084017894523</v>
+        <v>749.0040178945229</v>
       </c>
       <c r="E21" t="n">
-        <v>402.9505863572374</v>
+        <v>402.8705863572374</v>
       </c>
       <c r="F21" t="n">
-        <v>59.88367490483648</v>
+        <v>59.80367490483648</v>
       </c>
       <c r="G21" t="n">
-        <v>55.85669946408083</v>
+        <v>55.77669946408083</v>
       </c>
       <c r="H21" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I21" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J21" t="n">
-        <v>246.2912041375631</v>
+        <v>246.2112041375631</v>
       </c>
       <c r="K21" t="n">
-        <v>555.8339306093051</v>
+        <v>555.753930609305</v>
       </c>
       <c r="L21" t="n">
-        <v>989.0096988082788</v>
+        <v>988.9296988082788</v>
       </c>
       <c r="M21" t="n">
-        <v>1263.932740551138</v>
+        <v>1263.852740551138</v>
       </c>
       <c r="N21" t="n">
-        <v>1591.05362421531</v>
+        <v>1590.97362421531</v>
       </c>
       <c r="O21" t="n">
-        <v>2007.422354200916</v>
+        <v>2007.342354200916</v>
       </c>
       <c r="P21" t="n">
-        <v>2262.271670368536</v>
+        <v>2262.191670368536</v>
       </c>
       <c r="Q21" t="n">
-        <v>2262.271670368536</v>
+        <v>2262.191670368536</v>
       </c>
       <c r="R21" t="n">
-        <v>2080.925925057003</v>
+        <v>2080.845925057003</v>
       </c>
       <c r="S21" t="n">
-        <v>1948.016319603899</v>
+        <v>1947.936319603898</v>
       </c>
       <c r="T21" t="n">
-        <v>1865.871540558192</v>
+        <v>1865.791540558192</v>
       </c>
       <c r="U21" t="n">
-        <v>1591.237652543431</v>
+        <v>1785.831104741727</v>
       </c>
       <c r="V21" t="n">
-        <v>1496.782433158057</v>
+        <v>1691.375885356353</v>
       </c>
       <c r="W21" t="n">
-        <v>1384.284309006715</v>
+        <v>1578.877761205011</v>
       </c>
       <c r="X21" t="n">
-        <v>1284.422956031576</v>
+        <v>1479.016408229872</v>
       </c>
       <c r="Y21" t="n">
-        <v>1205.239731015279</v>
+        <v>1399.833183213575</v>
       </c>
     </row>
     <row r="22">
@@ -5877,76 +5877,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>686.6904483778065</v>
+        <v>686.6104483778066</v>
       </c>
       <c r="C22" t="n">
-        <v>734.4824541962423</v>
+        <v>734.4024541962424</v>
       </c>
       <c r="D22" t="n">
-        <v>769.5915983212424</v>
+        <v>769.5115983212424</v>
       </c>
       <c r="E22" t="n">
-        <v>809.2105025326554</v>
+        <v>809.1305025326554</v>
       </c>
       <c r="F22" t="n">
-        <v>855.3614751245908</v>
+        <v>855.2814751245909</v>
       </c>
       <c r="G22" t="n">
-        <v>931.1828770770499</v>
+        <v>931.1028770770499</v>
       </c>
       <c r="H22" t="n">
-        <v>1028.044822892185</v>
+        <v>1027.964822892185</v>
       </c>
       <c r="I22" t="n">
-        <v>1189.758226418432</v>
+        <v>1189.678226418432</v>
       </c>
       <c r="J22" t="n">
-        <v>1505.704370025436</v>
+        <v>1505.624370025436</v>
       </c>
       <c r="K22" t="n">
-        <v>1610.453394126239</v>
+        <v>1610.373394126239</v>
       </c>
       <c r="L22" t="n">
-        <v>1601.652180057278</v>
+        <v>1601.572180057279</v>
       </c>
       <c r="M22" t="n">
-        <v>1499.938679551308</v>
+        <v>1499.858679551308</v>
       </c>
       <c r="N22" t="n">
-        <v>1344.784852898339</v>
+        <v>1344.704852898339</v>
       </c>
       <c r="O22" t="n">
-        <v>1112.223511470621</v>
+        <v>1112.143511470621</v>
       </c>
       <c r="P22" t="n">
-        <v>819.1796012698439</v>
+        <v>819.0996012698439</v>
       </c>
       <c r="Q22" t="n">
-        <v>463.6348877086338</v>
+        <v>463.5548877086338</v>
       </c>
       <c r="R22" t="n">
-        <v>82.60111047978445</v>
+        <v>82.52111047978445</v>
       </c>
       <c r="S22" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="T22" t="n">
-        <v>164.4554332571655</v>
+        <v>164.3754332571655</v>
       </c>
       <c r="U22" t="n">
-        <v>332.8307078626652</v>
+        <v>332.7507078626653</v>
       </c>
       <c r="V22" t="n">
-        <v>453.4421007486112</v>
+        <v>453.3621007486113</v>
       </c>
       <c r="W22" t="n">
-        <v>547.1230190082886</v>
+        <v>547.0430190082886</v>
       </c>
       <c r="X22" t="n">
-        <v>619.9438100324821</v>
+        <v>619.8638100324822</v>
       </c>
       <c r="Y22" t="n">
-        <v>653.1431107115144</v>
+        <v>653.0631107115145</v>
       </c>
     </row>
     <row r="23">
@@ -5956,76 +5956,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>596.3814637549632</v>
+        <v>593.7843919601175</v>
       </c>
       <c r="C23" t="n">
-        <v>466.6091624994138</v>
+        <v>464.0120907045681</v>
       </c>
       <c r="D23" t="n">
-        <v>376.36759104502</v>
+        <v>373.7705192501743</v>
       </c>
       <c r="E23" t="n">
-        <v>292.162248007779</v>
+        <v>289.5651762129333</v>
       </c>
       <c r="F23" t="n">
-        <v>207.4252493128175</v>
+        <v>204.8281775179718</v>
       </c>
       <c r="G23" t="n">
-        <v>125.2531916248005</v>
+        <v>122.6561198299548</v>
       </c>
       <c r="H23" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I23" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J23" t="n">
-        <v>135.4535720585666</v>
+        <v>561.3752612788618</v>
       </c>
       <c r="K23" t="n">
-        <v>312.6439213047977</v>
+        <v>738.5656105250929</v>
       </c>
       <c r="L23" t="n">
-        <v>532.4642177872098</v>
+        <v>958.385907007505</v>
       </c>
       <c r="M23" t="n">
-        <v>1174.97421778721</v>
+        <v>1599.905907007505</v>
       </c>
       <c r="N23" t="n">
-        <v>1817.48421778721</v>
+        <v>1637.796970190582</v>
       </c>
       <c r="O23" t="n">
-        <v>1982.637728918909</v>
+        <v>1802.950481322281</v>
       </c>
       <c r="P23" t="n">
-        <v>2182.663622393207</v>
+        <v>2002.976374796579</v>
       </c>
       <c r="Q23" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="R23" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="S23" t="n">
-        <v>2451.379542772653</v>
+        <v>2448.782470977807</v>
       </c>
       <c r="T23" t="n">
-        <v>2189.241880907853</v>
+        <v>2186.644809113007</v>
       </c>
       <c r="U23" t="n">
-        <v>1857.81891753963</v>
+        <v>1855.221845744784</v>
       </c>
       <c r="V23" t="n">
-        <v>1545.84818605799</v>
+        <v>1543.251114263144</v>
       </c>
       <c r="W23" t="n">
-        <v>1225.268917390366</v>
+        <v>1222.67184559552</v>
       </c>
       <c r="X23" t="n">
-        <v>951.2468633896915</v>
+        <v>948.6497915948457</v>
       </c>
       <c r="Y23" t="n">
-        <v>759.0070323969577</v>
+        <v>756.4099606021121</v>
       </c>
     </row>
     <row r="24">
@@ -6035,76 +6035,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>168.3139162210097</v>
+        <v>168.2339162210096</v>
       </c>
       <c r="C24" t="n">
-        <v>127.8089541548285</v>
+        <v>127.7289541548285</v>
       </c>
       <c r="D24" t="n">
-        <v>100.5991694096744</v>
+        <v>100.5191694096743</v>
       </c>
       <c r="E24" t="n">
-        <v>78.70816211481312</v>
+        <v>78.62816211481311</v>
       </c>
       <c r="F24" t="n">
-        <v>59.88367490483648</v>
+        <v>59.80367490483648</v>
       </c>
       <c r="G24" t="n">
-        <v>55.85669946408083</v>
+        <v>55.77669946408083</v>
       </c>
       <c r="H24" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I24" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J24" t="n">
-        <v>246.2912041375631</v>
+        <v>246.2112041375631</v>
       </c>
       <c r="K24" t="n">
-        <v>555.8339306093051</v>
+        <v>555.753930609305</v>
       </c>
       <c r="L24" t="n">
-        <v>989.0096988082788</v>
+        <v>988.9296988082788</v>
       </c>
       <c r="M24" t="n">
-        <v>1263.932740551138</v>
+        <v>1263.852740551138</v>
       </c>
       <c r="N24" t="n">
-        <v>1591.05362421531</v>
+        <v>1590.97362421531</v>
       </c>
       <c r="O24" t="n">
-        <v>2007.422354200916</v>
+        <v>2007.342354200916</v>
       </c>
       <c r="P24" t="n">
-        <v>2262.271670368536</v>
+        <v>2262.191670368536</v>
       </c>
       <c r="Q24" t="n">
-        <v>2184.512931092847</v>
+        <v>2262.191670368536</v>
       </c>
       <c r="R24" t="n">
-        <v>1678.92476153889</v>
+        <v>2080.845925057003</v>
       </c>
       <c r="S24" t="n">
-        <v>1221.772731843361</v>
+        <v>1947.936319603898</v>
       </c>
       <c r="T24" t="n">
-        <v>1139.627952797655</v>
+        <v>1865.791540558192</v>
       </c>
       <c r="U24" t="n">
-        <v>735.4250927387657</v>
+        <v>1591.157652543431</v>
       </c>
       <c r="V24" t="n">
-        <v>640.9698733533918</v>
+        <v>1172.460008915633</v>
       </c>
       <c r="W24" t="n">
-        <v>411.5570362794425</v>
+        <v>735.7194605218667</v>
       </c>
       <c r="X24" t="n">
-        <v>311.6956833043036</v>
+        <v>311.6156833043036</v>
       </c>
       <c r="Y24" t="n">
-        <v>232.5124582880063</v>
+        <v>232.4324582880062</v>
       </c>
     </row>
     <row r="25">
@@ -6114,76 +6114,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>686.6904483778065</v>
+        <v>686.6104483778066</v>
       </c>
       <c r="C25" t="n">
-        <v>734.4824541962423</v>
+        <v>734.4024541962424</v>
       </c>
       <c r="D25" t="n">
-        <v>769.5915983212424</v>
+        <v>769.5115983212424</v>
       </c>
       <c r="E25" t="n">
-        <v>809.2105025326554</v>
+        <v>809.1305025326554</v>
       </c>
       <c r="F25" t="n">
-        <v>855.3614751245908</v>
+        <v>855.2814751245909</v>
       </c>
       <c r="G25" t="n">
-        <v>931.1828770770499</v>
+        <v>931.1028770770499</v>
       </c>
       <c r="H25" t="n">
-        <v>1028.044822892185</v>
+        <v>1027.964822892185</v>
       </c>
       <c r="I25" t="n">
-        <v>1189.758226418432</v>
+        <v>1189.678226418432</v>
       </c>
       <c r="J25" t="n">
-        <v>1516.807876906949</v>
+        <v>1505.624370025436</v>
       </c>
       <c r="K25" t="n">
-        <v>1610.453394126239</v>
+        <v>1610.373394126239</v>
       </c>
       <c r="L25" t="n">
-        <v>1601.652180057278</v>
+        <v>1601.572180057279</v>
       </c>
       <c r="M25" t="n">
-        <v>1499.938679551308</v>
+        <v>1499.858679551308</v>
       </c>
       <c r="N25" t="n">
-        <v>1344.784852898339</v>
+        <v>1344.704852898339</v>
       </c>
       <c r="O25" t="n">
-        <v>1112.223511470621</v>
+        <v>1112.143511470621</v>
       </c>
       <c r="P25" t="n">
-        <v>819.1796012698439</v>
+        <v>819.0996012698439</v>
       </c>
       <c r="Q25" t="n">
-        <v>463.6348877086338</v>
+        <v>463.5548877086338</v>
       </c>
       <c r="R25" t="n">
-        <v>82.60111047978445</v>
+        <v>82.52111047978445</v>
       </c>
       <c r="S25" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="T25" t="n">
-        <v>164.4554332571655</v>
+        <v>164.3754332571655</v>
       </c>
       <c r="U25" t="n">
-        <v>332.8307078626652</v>
+        <v>332.7507078626653</v>
       </c>
       <c r="V25" t="n">
-        <v>453.4421007486112</v>
+        <v>453.3621007486113</v>
       </c>
       <c r="W25" t="n">
-        <v>547.1230190082886</v>
+        <v>547.0430190082886</v>
       </c>
       <c r="X25" t="n">
-        <v>619.9438100324821</v>
+        <v>619.8638100324822</v>
       </c>
       <c r="Y25" t="n">
-        <v>653.1431107115144</v>
+        <v>653.0631107115145</v>
       </c>
     </row>
     <row r="26">
@@ -6193,37 +6193,37 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>596.4614637549632</v>
+        <v>601.7843919601175</v>
       </c>
       <c r="C26" t="n">
-        <v>466.6891624994138</v>
+        <v>472.0120907045681</v>
       </c>
       <c r="D26" t="n">
-        <v>376.4475910450201</v>
+        <v>381.7705192501743</v>
       </c>
       <c r="E26" t="n">
-        <v>292.242248007779</v>
+        <v>297.5651762129333</v>
       </c>
       <c r="F26" t="n">
-        <v>207.5052493128175</v>
+        <v>212.8281775179718</v>
       </c>
       <c r="G26" t="n">
-        <v>125.3331916248005</v>
+        <v>130.6561198299548</v>
       </c>
       <c r="H26" t="n">
-        <v>52</v>
+        <v>57.32292820515431</v>
       </c>
       <c r="I26" t="n">
         <v>52</v>
       </c>
       <c r="J26" t="n">
-        <v>561.5352612788618</v>
+        <v>135.5335720585666</v>
       </c>
       <c r="K26" t="n">
-        <v>738.7256105250929</v>
+        <v>312.7239213047977</v>
       </c>
       <c r="L26" t="n">
-        <v>958.545907007505</v>
+        <v>947.8205953940028</v>
       </c>
       <c r="M26" t="n">
         <v>1591.320595394003</v>
@@ -6241,28 +6241,28 @@
         <v>2600</v>
       </c>
       <c r="R26" t="n">
-        <v>2594.677071794846</v>
+        <v>2600</v>
       </c>
       <c r="S26" t="n">
-        <v>2451.459542772653</v>
+        <v>2456.782470977807</v>
       </c>
       <c r="T26" t="n">
-        <v>2189.321880907853</v>
+        <v>2194.644809113007</v>
       </c>
       <c r="U26" t="n">
-        <v>1857.89891753963</v>
+        <v>1863.221845744784</v>
       </c>
       <c r="V26" t="n">
-        <v>1545.92818605799</v>
+        <v>1551.251114263144</v>
       </c>
       <c r="W26" t="n">
-        <v>1225.348917390366</v>
+        <v>1230.67184559552</v>
       </c>
       <c r="X26" t="n">
-        <v>951.3268633896914</v>
+        <v>956.6497915948457</v>
       </c>
       <c r="Y26" t="n">
-        <v>759.0870323969577</v>
+        <v>764.4099606021121</v>
       </c>
     </row>
     <row r="27">
@@ -6272,25 +6272,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1010.016718817569</v>
+        <v>687.3097926617299</v>
       </c>
       <c r="C27" t="n">
-        <v>969.511756751388</v>
+        <v>452.1313783972528</v>
       </c>
       <c r="D27" t="n">
-        <v>942.3019720062339</v>
+        <v>424.9215936520986</v>
       </c>
       <c r="E27" t="n">
-        <v>596.1685404689483</v>
+        <v>78.7881621148131</v>
       </c>
       <c r="F27" t="n">
-        <v>253.1016290165474</v>
+        <v>59.96367490483648</v>
       </c>
       <c r="G27" t="n">
-        <v>249.0746535757918</v>
+        <v>55.93669946408082</v>
       </c>
       <c r="H27" t="n">
-        <v>245.1379541117109</v>
+        <v>52</v>
       </c>
       <c r="I27" t="n">
         <v>52</v>
@@ -6320,28 +6320,28 @@
         <v>2262.351670368536</v>
       </c>
       <c r="R27" t="n">
-        <v>1756.763500814579</v>
+        <v>2081.005925057003</v>
       </c>
       <c r="S27" t="n">
-        <v>1622.318397274889</v>
+        <v>1948.096319603899</v>
       </c>
       <c r="T27" t="n">
-        <v>1540.173618229182</v>
+        <v>1865.951540558192</v>
       </c>
       <c r="U27" t="n">
-        <v>1460.213182412718</v>
+        <v>1785.991104741727</v>
       </c>
       <c r="V27" t="n">
-        <v>1365.757963027344</v>
+        <v>1691.535885356353</v>
       </c>
       <c r="W27" t="n">
-        <v>1253.259838876002</v>
+        <v>1579.037761205011</v>
       </c>
       <c r="X27" t="n">
-        <v>1153.398485900863</v>
+        <v>1154.933983987448</v>
       </c>
       <c r="Y27" t="n">
-        <v>1074.215260884566</v>
+        <v>1075.750758971151</v>
       </c>
     </row>
     <row r="28">
@@ -6351,16 +6351,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>686.7704483778067</v>
+        <v>675.6669414962937</v>
       </c>
       <c r="C28" t="n">
-        <v>734.5624541962425</v>
+        <v>723.4589473147295</v>
       </c>
       <c r="D28" t="n">
-        <v>769.6715983212425</v>
+        <v>758.5680914397295</v>
       </c>
       <c r="E28" t="n">
-        <v>809.2905025326555</v>
+        <v>798.1869956511425</v>
       </c>
       <c r="F28" t="n">
         <v>844.337968243078</v>
@@ -6396,31 +6396,31 @@
         <v>819.2596012698439</v>
       </c>
       <c r="Q28" t="n">
-        <v>463.7148877086339</v>
+        <v>463.7148877086338</v>
       </c>
       <c r="R28" t="n">
-        <v>82.68111047978442</v>
+        <v>82.68111047978445</v>
       </c>
       <c r="S28" t="n">
         <v>52</v>
       </c>
       <c r="T28" t="n">
-        <v>164.5354332571655</v>
+        <v>153.4319263756526</v>
       </c>
       <c r="U28" t="n">
-        <v>332.9107078626653</v>
+        <v>321.8072009811523</v>
       </c>
       <c r="V28" t="n">
-        <v>453.5221007486113</v>
+        <v>442.4185938670983</v>
       </c>
       <c r="W28" t="n">
-        <v>547.2030190082887</v>
+        <v>536.0995121267757</v>
       </c>
       <c r="X28" t="n">
-        <v>620.0238100324823</v>
+        <v>608.9203031509693</v>
       </c>
       <c r="Y28" t="n">
-        <v>653.2231107115146</v>
+        <v>642.1196038300016</v>
       </c>
     </row>
     <row r="29">
@@ -6436,7 +6436,7 @@
         <v>466.6891624994138</v>
       </c>
       <c r="D29" t="n">
-        <v>376.44759104502</v>
+        <v>376.4475910450201</v>
       </c>
       <c r="E29" t="n">
         <v>292.242248007779</v>
@@ -6454,13 +6454,13 @@
         <v>52</v>
       </c>
       <c r="J29" t="n">
-        <v>561.5352612788618</v>
+        <v>135.5335720585666</v>
       </c>
       <c r="K29" t="n">
-        <v>738.7256105250929</v>
+        <v>312.7239213047977</v>
       </c>
       <c r="L29" t="n">
-        <v>958.545907007505</v>
+        <v>947.8205953940028</v>
       </c>
       <c r="M29" t="n">
         <v>1591.320595394003</v>
@@ -6478,7 +6478,7 @@
         <v>2600</v>
       </c>
       <c r="R29" t="n">
-        <v>2594.677071794846</v>
+        <v>2600</v>
       </c>
       <c r="S29" t="n">
         <v>2451.459542772653</v>
@@ -6509,22 +6509,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>285.3086291436169</v>
+        <v>687.3097926617299</v>
       </c>
       <c r="C30" t="n">
-        <v>127.8889541548285</v>
+        <v>646.8048305955489</v>
       </c>
       <c r="D30" t="n">
-        <v>100.6791694096743</v>
+        <v>424.9215936520986</v>
       </c>
       <c r="E30" t="n">
-        <v>78.7881621148131</v>
+        <v>403.0305863572374</v>
       </c>
       <c r="F30" t="n">
-        <v>59.96367490483648</v>
+        <v>59.96367490483647</v>
       </c>
       <c r="G30" t="n">
-        <v>55.93669946408082</v>
+        <v>55.93669946408081</v>
       </c>
       <c r="H30" t="n">
         <v>52</v>
@@ -6554,31 +6554,31 @@
         <v>2262.351670368536</v>
       </c>
       <c r="Q30" t="n">
-        <v>2184.592931092847</v>
+        <v>2262.351670368536</v>
       </c>
       <c r="R30" t="n">
-        <v>1679.00476153889</v>
+        <v>2081.005925057003</v>
       </c>
       <c r="S30" t="n">
-        <v>1546.095156085786</v>
+        <v>1948.096319603899</v>
       </c>
       <c r="T30" t="n">
-        <v>1463.950377040079</v>
+        <v>1865.951540558192</v>
       </c>
       <c r="U30" t="n">
-        <v>1059.74751698119</v>
+        <v>1785.991104741727</v>
       </c>
       <c r="V30" t="n">
-        <v>965.292297595816</v>
+        <v>1367.293461113929</v>
       </c>
       <c r="W30" t="n">
-        <v>852.794173444474</v>
+        <v>930.5529127201628</v>
       </c>
       <c r="X30" t="n">
-        <v>752.9328204693351</v>
+        <v>830.6915597450238</v>
       </c>
       <c r="Y30" t="n">
-        <v>673.7495954530377</v>
+        <v>751.5083347287265</v>
       </c>
     </row>
     <row r="31">
@@ -6591,10 +6591,10 @@
         <v>686.7704483778067</v>
       </c>
       <c r="C31" t="n">
-        <v>723.4589473147295</v>
+        <v>734.5624541962425</v>
       </c>
       <c r="D31" t="n">
-        <v>758.5680914397295</v>
+        <v>769.6715983212425</v>
       </c>
       <c r="E31" t="n">
         <v>798.1869956511425</v>
@@ -6633,10 +6633,10 @@
         <v>819.2596012698439</v>
       </c>
       <c r="Q31" t="n">
-        <v>463.7148877086338</v>
+        <v>463.7148877086339</v>
       </c>
       <c r="R31" t="n">
-        <v>82.68111047978445</v>
+        <v>82.68111047978442</v>
       </c>
       <c r="S31" t="n">
         <v>52</v>
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>601.7843919601175</v>
+        <v>596.4614637549632</v>
       </c>
       <c r="C32" t="n">
-        <v>472.0120907045681</v>
+        <v>466.6891624994138</v>
       </c>
       <c r="D32" t="n">
-        <v>381.7705192501743</v>
+        <v>376.44759104502</v>
       </c>
       <c r="E32" t="n">
-        <v>297.5651762129333</v>
+        <v>292.242248007779</v>
       </c>
       <c r="F32" t="n">
-        <v>212.8281775179718</v>
+        <v>207.5052493128175</v>
       </c>
       <c r="G32" t="n">
-        <v>130.6561198299548</v>
+        <v>125.3331916248005</v>
       </c>
       <c r="H32" t="n">
-        <v>57.32292820515428</v>
+        <v>52</v>
       </c>
       <c r="I32" t="n">
         <v>52</v>
       </c>
       <c r="J32" t="n">
-        <v>561.5352612788618</v>
+        <v>135.5335720585666</v>
       </c>
       <c r="K32" t="n">
-        <v>738.7256105250929</v>
+        <v>312.7239213047977</v>
       </c>
       <c r="L32" t="n">
-        <v>958.545907007505</v>
+        <v>532.5442177872098</v>
       </c>
       <c r="M32" t="n">
-        <v>958.5459070075051</v>
+        <v>1002.296970190582</v>
       </c>
       <c r="N32" t="n">
-        <v>1602.045907007505</v>
+        <v>1645.796970190582</v>
       </c>
       <c r="O32" t="n">
-        <v>1956.5</v>
+        <v>1810.950481322281</v>
       </c>
       <c r="P32" t="n">
-        <v>2600</v>
+        <v>2010.976374796579</v>
       </c>
       <c r="Q32" t="n">
         <v>2600</v>
       </c>
       <c r="R32" t="n">
-        <v>2600</v>
+        <v>2594.677071794846</v>
       </c>
       <c r="S32" t="n">
-        <v>2456.782470977807</v>
+        <v>2451.459542772653</v>
       </c>
       <c r="T32" t="n">
-        <v>2194.644809113007</v>
+        <v>2189.321880907853</v>
       </c>
       <c r="U32" t="n">
-        <v>1863.221845744784</v>
+        <v>1857.89891753963</v>
       </c>
       <c r="V32" t="n">
-        <v>1551.251114263144</v>
+        <v>1545.92818605799</v>
       </c>
       <c r="W32" t="n">
-        <v>1230.67184559552</v>
+        <v>1225.348917390366</v>
       </c>
       <c r="X32" t="n">
-        <v>956.6497915948457</v>
+        <v>951.3268633896914</v>
       </c>
       <c r="Y32" t="n">
-        <v>764.4099606021121</v>
+        <v>759.0870323969577</v>
       </c>
     </row>
     <row r="33">
@@ -6746,22 +6746,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>168.3939162210096</v>
+        <v>816.8787647058581</v>
       </c>
       <c r="C33" t="n">
-        <v>127.8889541548285</v>
+        <v>776.373802639677</v>
       </c>
       <c r="D33" t="n">
-        <v>100.6791694096743</v>
+        <v>424.9215936520986</v>
       </c>
       <c r="E33" t="n">
         <v>78.7881621148131</v>
       </c>
       <c r="F33" t="n">
-        <v>59.96367490483647</v>
+        <v>59.96367490483648</v>
       </c>
       <c r="G33" t="n">
-        <v>55.93669946408081</v>
+        <v>55.93669946408082</v>
       </c>
       <c r="H33" t="n">
         <v>52</v>
@@ -6794,28 +6794,28 @@
         <v>2262.351670368536</v>
       </c>
       <c r="R33" t="n">
-        <v>2081.005925057003</v>
+        <v>1756.763500814579</v>
       </c>
       <c r="S33" t="n">
-        <v>1948.096319603899</v>
+        <v>1429.180443163178</v>
       </c>
       <c r="T33" t="n">
-        <v>1865.951540558192</v>
+        <v>1347.035664117471</v>
       </c>
       <c r="U33" t="n">
-        <v>1591.317652543431</v>
+        <v>1267.075228301007</v>
       </c>
       <c r="V33" t="n">
         <v>1172.620008915633</v>
       </c>
       <c r="W33" t="n">
-        <v>735.8794605218668</v>
+        <v>1060.121884764291</v>
       </c>
       <c r="X33" t="n">
-        <v>311.7756833043036</v>
+        <v>960.260531789152</v>
       </c>
       <c r="Y33" t="n">
-        <v>232.5924582880062</v>
+        <v>881.0773067728546</v>
       </c>
     </row>
     <row r="34">
@@ -6837,16 +6837,16 @@
         <v>809.2905025326555</v>
       </c>
       <c r="F34" t="n">
-        <v>844.337968243078</v>
+        <v>855.441475124591</v>
       </c>
       <c r="G34" t="n">
-        <v>920.159370195537</v>
+        <v>931.26287707705</v>
       </c>
       <c r="H34" t="n">
-        <v>1017.021316010672</v>
+        <v>1028.124822892185</v>
       </c>
       <c r="I34" t="n">
-        <v>1178.734719536919</v>
+        <v>1189.838226418432</v>
       </c>
       <c r="J34" t="n">
         <v>1505.784370025436</v>
@@ -6870,10 +6870,10 @@
         <v>819.2596012698439</v>
       </c>
       <c r="Q34" t="n">
-        <v>463.7148877086339</v>
+        <v>463.7148877086338</v>
       </c>
       <c r="R34" t="n">
-        <v>82.68111047978442</v>
+        <v>82.68111047978445</v>
       </c>
       <c r="S34" t="n">
         <v>52</v>
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>431.7237858995115</v>
+        <v>443.6429778187036</v>
       </c>
       <c r="C35" t="n">
-        <v>326.1939088863863</v>
+        <v>337.1029997954774</v>
       </c>
       <c r="D35" t="n">
-        <v>260.1947616744168</v>
+        <v>270.093751573407</v>
       </c>
       <c r="E35" t="n">
-        <v>200.2318428796</v>
+        <v>209.1207317684891</v>
       </c>
       <c r="F35" t="n">
-        <v>139.7372684270628</v>
+        <v>147.6160563058509</v>
       </c>
       <c r="G35" t="n">
-        <v>93.8107673823763</v>
+        <v>95.22086839247729</v>
       </c>
       <c r="H35" t="n">
-        <v>44.72</v>
+        <v>45.12</v>
       </c>
       <c r="I35" t="n">
-        <v>44.72</v>
+        <v>45.12</v>
       </c>
       <c r="J35" t="n">
-        <v>554.2552612788618</v>
+        <v>128.6535720585666</v>
       </c>
       <c r="K35" t="n">
-        <v>731.4456105250929</v>
+        <v>305.8439213047978</v>
       </c>
       <c r="L35" t="n">
-        <v>951.265907007505</v>
+        <v>525.6642177872099</v>
       </c>
       <c r="M35" t="n">
-        <v>1504.675907007514</v>
+        <v>1084.02421778721</v>
       </c>
       <c r="N35" t="n">
-        <v>1870.820595394003</v>
+        <v>1642.38421778721</v>
       </c>
       <c r="O35" t="n">
-        <v>2035.974106525702</v>
+        <v>1807.537728918908</v>
       </c>
       <c r="P35" t="n">
-        <v>2236</v>
+        <v>2007.563622393207</v>
       </c>
       <c r="Q35" t="n">
-        <v>2236</v>
+        <v>2256</v>
       </c>
       <c r="R35" t="n">
-        <v>2236</v>
+        <v>2256</v>
       </c>
       <c r="S35" t="n">
-        <v>2117.024895220231</v>
+        <v>2136.01479421013</v>
       </c>
       <c r="T35" t="n">
-        <v>1879.129657597855</v>
+        <v>1897.109455577654</v>
       </c>
       <c r="U35" t="n">
-        <v>1571.949118472057</v>
+        <v>1588.918815441754</v>
       </c>
       <c r="V35" t="n">
-        <v>1284.220811232841</v>
+        <v>1300.180407192437</v>
       </c>
       <c r="W35" t="n">
-        <v>987.8839668076414</v>
+        <v>1002.833461757137</v>
       </c>
       <c r="X35" t="n">
-        <v>738.1043370493912</v>
+        <v>752.0437309887853</v>
       </c>
       <c r="Y35" t="n">
-        <v>570.1069302990818</v>
+        <v>583.0362232283749</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1429.814213507527</v>
+        <v>722.8186237363738</v>
       </c>
       <c r="C36" t="n">
-        <v>1413.55167568377</v>
+        <v>705.5459849025159</v>
       </c>
       <c r="D36" t="n">
-        <v>1062.099466696191</v>
+        <v>701.568523389685</v>
       </c>
       <c r="E36" t="n">
-        <v>715.9660351589059</v>
+        <v>701.568523389685</v>
       </c>
       <c r="F36" t="n">
-        <v>372.8991237065051</v>
+        <v>701.568523389685</v>
       </c>
       <c r="G36" t="n">
-        <v>372.8991237065051</v>
+        <v>373.2991237065051</v>
       </c>
       <c r="H36" t="n">
-        <v>44.72</v>
+        <v>45.12</v>
       </c>
       <c r="I36" t="n">
-        <v>44.72</v>
+        <v>45.12</v>
       </c>
       <c r="J36" t="n">
-        <v>239.0912041375631</v>
+        <v>239.4912041375631</v>
       </c>
       <c r="K36" t="n">
-        <v>548.633930609305</v>
+        <v>549.033930609305</v>
       </c>
       <c r="L36" t="n">
-        <v>981.8096988082788</v>
+        <v>982.2096988082787</v>
       </c>
       <c r="M36" t="n">
-        <v>1237.661070182602</v>
+        <v>1257.132740551138</v>
       </c>
       <c r="N36" t="n">
-        <v>1564.781953846774</v>
+        <v>1584.25362421531</v>
       </c>
       <c r="O36" t="n">
-        <v>1981.15068383238</v>
+        <v>2000.622354200916</v>
       </c>
       <c r="P36" t="n">
-        <v>2236</v>
+        <v>2255.471670368536</v>
       </c>
       <c r="Q36" t="n">
-        <v>2158.241260724311</v>
+        <v>2177.712931092847</v>
       </c>
       <c r="R36" t="n">
-        <v>1981.086103478557</v>
+        <v>1672.12476153889</v>
       </c>
       <c r="S36" t="n">
-        <v>1872.418922267877</v>
+        <v>1214.972731843361</v>
       </c>
       <c r="T36" t="n">
-        <v>1814.516567464595</v>
+        <v>1156.060276029978</v>
       </c>
       <c r="U36" t="n">
-        <v>1758.798555890554</v>
+        <v>1099.332163445836</v>
       </c>
       <c r="V36" t="n">
-        <v>1688.585760747605</v>
+        <v>1028.109267292786</v>
       </c>
       <c r="W36" t="n">
-        <v>1600.330060838687</v>
+        <v>938.843466373767</v>
       </c>
       <c r="X36" t="n">
-        <v>1524.711132105972</v>
+        <v>862.2144366309512</v>
       </c>
       <c r="Y36" t="n">
-        <v>1469.770331332099</v>
+        <v>806.2635348469771</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>334.9035619476512</v>
+        <v>738.4774805251941</v>
       </c>
       <c r="C37" t="n">
-        <v>406.4555677660869</v>
+        <v>809.0394863436298</v>
       </c>
       <c r="D37" t="n">
-        <v>465.324711891087</v>
+        <v>866.9186304686299</v>
       </c>
       <c r="E37" t="n">
-        <v>465.324711891087</v>
+        <v>929.3075346800429</v>
       </c>
       <c r="F37" t="n">
-        <v>535.2356844830224</v>
+        <v>998.2285072719784</v>
       </c>
       <c r="G37" t="n">
-        <v>624.2072563385952</v>
+        <v>1096.819909224437</v>
       </c>
       <c r="H37" t="n">
-        <v>744.8292021537305</v>
+        <v>1096.819909224437</v>
       </c>
       <c r="I37" t="n">
-        <v>930.3026056799774</v>
+        <v>1281.303312750684</v>
       </c>
       <c r="J37" t="n">
-        <v>1281.112256168494</v>
+        <v>1290.562963239201</v>
       </c>
       <c r="K37" t="n">
-        <v>1409.621280269297</v>
+        <v>1418.081987340004</v>
       </c>
       <c r="L37" t="n">
-        <v>1424.755210360309</v>
+        <v>1432.225917431016</v>
       </c>
       <c r="M37" t="n">
-        <v>1347.284134096763</v>
+        <v>1353.744740157369</v>
       </c>
       <c r="N37" t="n">
-        <v>1216.372731686218</v>
+        <v>1221.823236736723</v>
       </c>
       <c r="O37" t="n">
-        <v>1008.053814500924</v>
+        <v>1012.494218541328</v>
       </c>
       <c r="P37" t="n">
-        <v>739.2523285425713</v>
+        <v>742.6826315728742</v>
       </c>
       <c r="Q37" t="n">
-        <v>407.9500392237854</v>
+        <v>410.3702412439874</v>
       </c>
       <c r="R37" t="n">
-        <v>51.15868623736019</v>
+        <v>52.56878724746122</v>
       </c>
       <c r="S37" t="n">
-        <v>44.72</v>
+        <v>45.12</v>
       </c>
       <c r="T37" t="n">
-        <v>181.0154332571655</v>
+        <v>180.4254332571655</v>
       </c>
       <c r="U37" t="n">
-        <v>181.0154332571655</v>
+        <v>371.5707078626653</v>
       </c>
       <c r="V37" t="n">
-        <v>181.0154332571655</v>
+        <v>414.1491328959988</v>
       </c>
       <c r="W37" t="n">
-        <v>181.0154332571655</v>
+        <v>530.6000511556762</v>
       </c>
       <c r="X37" t="n">
-        <v>277.596224281359</v>
+        <v>626.1908421798697</v>
       </c>
       <c r="Y37" t="n">
-        <v>277.596224281359</v>
+        <v>682.160142858902</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>431.7237858995115</v>
+        <v>443.6429778187041</v>
       </c>
       <c r="C38" t="n">
-        <v>326.1939088863863</v>
+        <v>337.1029997954779</v>
       </c>
       <c r="D38" t="n">
-        <v>260.1947616744168</v>
+        <v>270.0937515734074</v>
       </c>
       <c r="E38" t="n">
-        <v>200.2318428796</v>
+        <v>209.1207317684896</v>
       </c>
       <c r="F38" t="n">
-        <v>151.740400827969</v>
+        <v>154.1606028481711</v>
       </c>
       <c r="G38" t="n">
-        <v>93.8107673823763</v>
+        <v>95.22086839247731</v>
       </c>
       <c r="H38" t="n">
-        <v>44.72</v>
+        <v>45.12</v>
       </c>
       <c r="I38" t="n">
-        <v>44.72</v>
+        <v>45.12</v>
       </c>
       <c r="J38" t="n">
-        <v>554.2552612788618</v>
+        <v>128.6535720585666</v>
       </c>
       <c r="K38" t="n">
-        <v>1107.665261278862</v>
+        <v>305.8439213047978</v>
       </c>
       <c r="L38" t="n">
-        <v>1661.075261278862</v>
+        <v>864.2039213047977</v>
       </c>
       <c r="M38" t="n">
-        <v>1870.820595394003</v>
+        <v>1332.460595394003</v>
       </c>
       <c r="N38" t="n">
-        <v>1870.820595394003</v>
+        <v>1890.820595394003</v>
       </c>
       <c r="O38" t="n">
-        <v>2035.974106525702</v>
+        <v>2055.974106525702</v>
       </c>
       <c r="P38" t="n">
-        <v>2236</v>
+        <v>2256</v>
       </c>
       <c r="Q38" t="n">
-        <v>2236</v>
+        <v>2256</v>
       </c>
       <c r="R38" t="n">
-        <v>2236</v>
+        <v>2256</v>
       </c>
       <c r="S38" t="n">
-        <v>2117.024895220231</v>
+        <v>2136.01479421013</v>
       </c>
       <c r="T38" t="n">
-        <v>1879.129657597855</v>
+        <v>1897.109455577654</v>
       </c>
       <c r="U38" t="n">
-        <v>1571.949118472057</v>
+        <v>1588.918815441755</v>
       </c>
       <c r="V38" t="n">
-        <v>1284.220811232841</v>
+        <v>1300.180407192438</v>
       </c>
       <c r="W38" t="n">
-        <v>987.8839668076414</v>
+        <v>1002.833461757137</v>
       </c>
       <c r="X38" t="n">
-        <v>738.1043370493912</v>
+        <v>752.0437309887858</v>
       </c>
       <c r="Y38" t="n">
-        <v>570.1069302990818</v>
+        <v>583.0362232283753</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>720.3984217161717</v>
+        <v>66.37010034668882</v>
       </c>
       <c r="C39" t="n">
-        <v>704.1358838924149</v>
+        <v>49.09746151283094</v>
       </c>
       <c r="D39" t="n">
-        <v>701.168523389685</v>
+        <v>45.12</v>
       </c>
       <c r="E39" t="n">
-        <v>701.168523389685</v>
+        <v>45.12</v>
       </c>
       <c r="F39" t="n">
-        <v>701.168523389685</v>
+        <v>45.12</v>
       </c>
       <c r="G39" t="n">
-        <v>372.8991237065051</v>
+        <v>45.12</v>
       </c>
       <c r="H39" t="n">
-        <v>44.72</v>
+        <v>45.12</v>
       </c>
       <c r="I39" t="n">
-        <v>44.72</v>
+        <v>45.12</v>
       </c>
       <c r="J39" t="n">
-        <v>239.0912041375631</v>
+        <v>239.4912041375631</v>
       </c>
       <c r="K39" t="n">
-        <v>548.633930609305</v>
+        <v>549.033930609305</v>
       </c>
       <c r="L39" t="n">
-        <v>981.8096988082788</v>
+        <v>982.2096988082787</v>
       </c>
       <c r="M39" t="n">
-        <v>1237.661070182602</v>
+        <v>1257.132740551138</v>
       </c>
       <c r="N39" t="n">
-        <v>1564.781953846774</v>
+        <v>1584.25362421531</v>
       </c>
       <c r="O39" t="n">
-        <v>1981.15068383238</v>
+        <v>2000.622354200916</v>
       </c>
       <c r="P39" t="n">
-        <v>2236</v>
+        <v>2255.471670368536</v>
       </c>
       <c r="Q39" t="n">
-        <v>2236</v>
+        <v>2177.712931092847</v>
       </c>
       <c r="R39" t="n">
-        <v>2078.896678930892</v>
+        <v>1672.12476153889</v>
       </c>
       <c r="S39" t="n">
-        <v>1970.229497720212</v>
+        <v>1214.972731843361</v>
       </c>
       <c r="T39" t="n">
-        <v>1802.070472642937</v>
+        <v>808.5855285552302</v>
       </c>
       <c r="U39" t="n">
-        <v>1746.352461068896</v>
+        <v>747.8796952549689</v>
       </c>
       <c r="V39" t="n">
-        <v>1327.654817441098</v>
+        <v>676.6567991019182</v>
       </c>
       <c r="W39" t="n">
-        <v>1239.39911753218</v>
+        <v>587.3909981828995</v>
       </c>
       <c r="X39" t="n">
-        <v>815.2953403146171</v>
+        <v>163.2872209653362</v>
       </c>
       <c r="Y39" t="n">
-        <v>760.354539540744</v>
+        <v>107.3363191813622</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>708.1871320697502</v>
+        <v>560.5936222346951</v>
       </c>
       <c r="C40" t="n">
-        <v>779.739137888186</v>
+        <v>560.5936222346951</v>
       </c>
       <c r="D40" t="n">
-        <v>838.608282013186</v>
+        <v>618.4727663596951</v>
       </c>
       <c r="E40" t="n">
-        <v>838.608282013186</v>
+        <v>680.8616705711081</v>
       </c>
       <c r="F40" t="n">
-        <v>838.608282013186</v>
+        <v>749.7826431630435</v>
       </c>
       <c r="G40" t="n">
-        <v>938.189683965645</v>
+        <v>848.3740451155026</v>
       </c>
       <c r="H40" t="n">
-        <v>1058.81162978078</v>
+        <v>968.0059909306378</v>
       </c>
       <c r="I40" t="n">
-        <v>1058.81162978078</v>
+        <v>968.0059909306378</v>
       </c>
       <c r="J40" t="n">
-        <v>1409.621280269297</v>
+        <v>1317.825641419155</v>
       </c>
       <c r="K40" t="n">
-        <v>1409.621280269297</v>
+        <v>1432.225917431016</v>
       </c>
       <c r="L40" t="n">
-        <v>1424.755210360309</v>
+        <v>1432.225917431016</v>
       </c>
       <c r="M40" t="n">
-        <v>1347.284134096763</v>
+        <v>1353.744740157369</v>
       </c>
       <c r="N40" t="n">
-        <v>1216.372731686218</v>
+        <v>1221.823236736723</v>
       </c>
       <c r="O40" t="n">
-        <v>1008.053814500924</v>
+        <v>1012.494218541328</v>
       </c>
       <c r="P40" t="n">
-        <v>739.2523285425713</v>
+        <v>742.6826315728742</v>
       </c>
       <c r="Q40" t="n">
-        <v>407.9500392237854</v>
+        <v>410.3702412439874</v>
       </c>
       <c r="R40" t="n">
-        <v>51.15868623736019</v>
+        <v>52.5687872474612</v>
       </c>
       <c r="S40" t="n">
-        <v>44.72</v>
+        <v>45.12</v>
       </c>
       <c r="T40" t="n">
-        <v>181.0154332571655</v>
+        <v>45.12</v>
       </c>
       <c r="U40" t="n">
-        <v>373.1507078626653</v>
+        <v>236.2652746054998</v>
       </c>
       <c r="V40" t="n">
-        <v>379.8987844405549</v>
+        <v>236.2652746054998</v>
       </c>
       <c r="W40" t="n">
-        <v>497.3397027002323</v>
+        <v>352.7161928651772</v>
       </c>
       <c r="X40" t="n">
-        <v>593.9204937244258</v>
+        <v>448.3069838893707</v>
       </c>
       <c r="Y40" t="n">
-        <v>650.879794403458</v>
+        <v>504.276284568403</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>237.7843919601177</v>
+        <v>257.7843919601178</v>
       </c>
       <c r="C41" t="n">
-        <v>128.9253430372411</v>
+        <v>135.3615714543937</v>
       </c>
       <c r="D41" t="n">
-        <v>128.9253430372411</v>
+        <v>45.12</v>
       </c>
       <c r="E41" t="n">
-        <v>44.72</v>
+        <v>45.12</v>
       </c>
       <c r="F41" t="n">
-        <v>44.72</v>
+        <v>45.12</v>
       </c>
       <c r="G41" t="n">
-        <v>44.72</v>
+        <v>45.12</v>
       </c>
       <c r="H41" t="n">
-        <v>44.72</v>
+        <v>45.12</v>
       </c>
       <c r="I41" t="n">
-        <v>44.72</v>
+        <v>45.12</v>
       </c>
       <c r="J41" t="n">
-        <v>128.2535720585666</v>
+        <v>128.6535720585666</v>
       </c>
       <c r="K41" t="n">
-        <v>305.4439213047978</v>
+        <v>305.8439213047978</v>
       </c>
       <c r="L41" t="n">
-        <v>525.2642177872099</v>
+        <v>525.6642177872099</v>
       </c>
       <c r="M41" t="n">
-        <v>764.0005953939278</v>
+        <v>1084.02421778721</v>
       </c>
       <c r="N41" t="n">
-        <v>1317.410595393965</v>
+        <v>1642.38421778721</v>
       </c>
       <c r="O41" t="n">
-        <v>1482.564106525664</v>
+        <v>1807.537728918908</v>
       </c>
       <c r="P41" t="n">
-        <v>1682.589999999962</v>
+        <v>2007.563622393207</v>
       </c>
       <c r="Q41" t="n">
-        <v>2236</v>
+        <v>2256</v>
       </c>
       <c r="R41" t="n">
-        <v>2236</v>
+        <v>2256</v>
       </c>
       <c r="S41" t="n">
-        <v>2092.782470977807</v>
+        <v>2112.782470977807</v>
       </c>
       <c r="T41" t="n">
-        <v>1830.644809113007</v>
+        <v>1850.644809113007</v>
       </c>
       <c r="U41" t="n">
-        <v>1499.221845744785</v>
+        <v>1519.221845744785</v>
       </c>
       <c r="V41" t="n">
-        <v>1187.251114263144</v>
+        <v>1207.251114263144</v>
       </c>
       <c r="W41" t="n">
-        <v>866.6718455955204</v>
+        <v>886.6718455955204</v>
       </c>
       <c r="X41" t="n">
-        <v>592.649791594846</v>
+        <v>612.649791594846</v>
       </c>
       <c r="Y41" t="n">
-        <v>400.4099606021122</v>
+        <v>420.4099606021122</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>985.2005465356183</v>
+        <v>485.756340463434</v>
       </c>
       <c r="C42" t="n">
-        <v>944.6955844694372</v>
+        <v>445.2513783972528</v>
       </c>
       <c r="D42" t="n">
-        <v>741.8840178945228</v>
+        <v>418.0415936520986</v>
       </c>
       <c r="E42" t="n">
-        <v>719.9930105996616</v>
+        <v>396.1505863572374</v>
       </c>
       <c r="F42" t="n">
-        <v>376.9260991472607</v>
+        <v>377.3260991472608</v>
       </c>
       <c r="G42" t="n">
-        <v>372.8991237065051</v>
+        <v>373.2991237065051</v>
       </c>
       <c r="H42" t="n">
-        <v>44.72</v>
+        <v>45.12</v>
       </c>
       <c r="I42" t="n">
-        <v>44.72</v>
+        <v>45.12</v>
       </c>
       <c r="J42" t="n">
-        <v>239.0912041375631</v>
+        <v>239.4912041375631</v>
       </c>
       <c r="K42" t="n">
-        <v>548.633930609305</v>
+        <v>549.033930609305</v>
       </c>
       <c r="L42" t="n">
-        <v>962.7380284397429</v>
+        <v>982.2096988082787</v>
       </c>
       <c r="M42" t="n">
-        <v>1237.661070182602</v>
+        <v>1257.132740551138</v>
       </c>
       <c r="N42" t="n">
-        <v>1564.781953846774</v>
+        <v>1584.25362421531</v>
       </c>
       <c r="O42" t="n">
-        <v>1981.15068383238</v>
+        <v>2000.622354200916</v>
       </c>
       <c r="P42" t="n">
-        <v>2236</v>
+        <v>2255.471670368536</v>
       </c>
       <c r="Q42" t="n">
-        <v>2236</v>
+        <v>2255.471670368536</v>
       </c>
       <c r="R42" t="n">
-        <v>2054.654254688468</v>
+        <v>1879.452472858708</v>
       </c>
       <c r="S42" t="n">
-        <v>1921.744649235363</v>
+        <v>1746.542867405603</v>
       </c>
       <c r="T42" t="n">
-        <v>1839.599870189656</v>
+        <v>1664.398088359896</v>
       </c>
       <c r="U42" t="n">
-        <v>1759.639434373191</v>
+        <v>1584.437652543431</v>
       </c>
       <c r="V42" t="n">
-        <v>1665.184214987817</v>
+        <v>1165.740008915633</v>
       </c>
       <c r="W42" t="n">
-        <v>1552.686090836475</v>
+        <v>1053.241884764291</v>
       </c>
       <c r="X42" t="n">
-        <v>1452.824737861336</v>
+        <v>629.1381075467278</v>
       </c>
       <c r="Y42" t="n">
-        <v>1373.641512845039</v>
+        <v>549.9548825304305</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>668.386941496294</v>
+        <v>668.7869414962938</v>
       </c>
       <c r="C43" t="n">
-        <v>716.1789473147297</v>
+        <v>716.5789473147296</v>
       </c>
       <c r="D43" t="n">
-        <v>751.2880914397298</v>
+        <v>751.6880914397296</v>
       </c>
       <c r="E43" t="n">
-        <v>790.9069956511428</v>
+        <v>791.3069956511426</v>
       </c>
       <c r="F43" t="n">
-        <v>837.0579682430782</v>
+        <v>837.4579682430781</v>
       </c>
       <c r="G43" t="n">
-        <v>912.8793701955373</v>
+        <v>913.2793701955371</v>
       </c>
       <c r="H43" t="n">
-        <v>1009.741316010673</v>
+        <v>1010.141316010672</v>
       </c>
       <c r="I43" t="n">
-        <v>1171.454719536919</v>
+        <v>1171.854719536919</v>
       </c>
       <c r="J43" t="n">
-        <v>1498.504370025436</v>
+        <v>1498.904370025436</v>
       </c>
       <c r="K43" t="n">
-        <v>1603.253394126239</v>
+        <v>1603.653394126239</v>
       </c>
       <c r="L43" t="n">
-        <v>1594.452180057278</v>
+        <v>1594.852180057278</v>
       </c>
       <c r="M43" t="n">
-        <v>1492.738679551308</v>
+        <v>1493.138679551308</v>
       </c>
       <c r="N43" t="n">
-        <v>1337.584852898339</v>
+        <v>1337.984852898339</v>
       </c>
       <c r="O43" t="n">
-        <v>1105.023511470621</v>
+        <v>1105.423511470621</v>
       </c>
       <c r="P43" t="n">
-        <v>811.9796012698439</v>
+        <v>812.3796012698439</v>
       </c>
       <c r="Q43" t="n">
-        <v>456.4348877086338</v>
+        <v>456.8348877086338</v>
       </c>
       <c r="R43" t="n">
-        <v>75.40111047978442</v>
+        <v>75.80111047978446</v>
       </c>
       <c r="S43" t="n">
-        <v>44.72</v>
+        <v>45.12</v>
       </c>
       <c r="T43" t="n">
-        <v>146.1519263756528</v>
+        <v>157.6554332571655</v>
       </c>
       <c r="U43" t="n">
-        <v>314.5272009811526</v>
+        <v>314.9272009811525</v>
       </c>
       <c r="V43" t="n">
-        <v>435.1385938670986</v>
+        <v>435.5385938670984</v>
       </c>
       <c r="W43" t="n">
-        <v>528.819512126776</v>
+        <v>529.2195121267758</v>
       </c>
       <c r="X43" t="n">
-        <v>601.6403031509695</v>
+        <v>602.0403031509694</v>
       </c>
       <c r="Y43" t="n">
-        <v>634.8396038300018</v>
+        <v>635.2396038300017</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>381.0019209825873</v>
+        <v>257.7843919601178</v>
       </c>
       <c r="C44" t="n">
-        <v>381.0019209825873</v>
+        <v>128.0120907045684</v>
       </c>
       <c r="D44" t="n">
-        <v>290.7603495281936</v>
+        <v>45.12</v>
       </c>
       <c r="E44" t="n">
-        <v>284.962248007779</v>
+        <v>45.12</v>
       </c>
       <c r="F44" t="n">
-        <v>200.2252493128175</v>
+        <v>45.12</v>
       </c>
       <c r="G44" t="n">
-        <v>118.0531916248005</v>
+        <v>45.12</v>
       </c>
       <c r="H44" t="n">
-        <v>44.72</v>
+        <v>45.12</v>
       </c>
       <c r="I44" t="n">
-        <v>44.72</v>
+        <v>45.12</v>
       </c>
       <c r="J44" t="n">
-        <v>128.2535720585666</v>
+        <v>128.6535720585666</v>
       </c>
       <c r="K44" t="n">
-        <v>305.4439213047978</v>
+        <v>305.8439213047978</v>
       </c>
       <c r="L44" t="n">
-        <v>525.2642177872099</v>
+        <v>525.6642177872099</v>
       </c>
       <c r="M44" t="n">
-        <v>1078.674217787276</v>
+        <v>1084.02421778721</v>
       </c>
       <c r="N44" t="n">
-        <v>1632.084217787342</v>
+        <v>1332.460595394003</v>
       </c>
       <c r="O44" t="n">
-        <v>1797.237728919041</v>
+        <v>1497.614106525702</v>
       </c>
       <c r="P44" t="n">
-        <v>1997.263622393339</v>
+        <v>1697.64</v>
       </c>
       <c r="Q44" t="n">
-        <v>2236.000000000276</v>
+        <v>2256</v>
       </c>
       <c r="R44" t="n">
-        <v>2236.000000000276</v>
+        <v>2256</v>
       </c>
       <c r="S44" t="n">
-        <v>2236.000000000276</v>
+        <v>2112.782470977807</v>
       </c>
       <c r="T44" t="n">
-        <v>1973.862338135477</v>
+        <v>1850.644809113007</v>
       </c>
       <c r="U44" t="n">
-        <v>1642.439374767254</v>
+        <v>1519.221845744785</v>
       </c>
       <c r="V44" t="n">
-        <v>1330.468643285614</v>
+        <v>1207.251114263144</v>
       </c>
       <c r="W44" t="n">
-        <v>1009.88937461799</v>
+        <v>886.6718455955204</v>
       </c>
       <c r="X44" t="n">
-        <v>735.8673206173155</v>
+        <v>612.649791594846</v>
       </c>
       <c r="Y44" t="n">
-        <v>543.6274896245818</v>
+        <v>420.4099606021122</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>660.9581222934709</v>
+        <v>1004.672216904154</v>
       </c>
       <c r="C45" t="n">
-        <v>620.4531602272898</v>
+        <v>639.9248305955489</v>
       </c>
       <c r="D45" t="n">
-        <v>593.2433754821357</v>
+        <v>612.7150458503947</v>
       </c>
       <c r="E45" t="n">
-        <v>571.3523681872745</v>
+        <v>396.1505863572374</v>
       </c>
       <c r="F45" t="n">
-        <v>245.8216290165474</v>
+        <v>53.08367490483649</v>
       </c>
       <c r="G45" t="n">
-        <v>241.7946535757918</v>
+        <v>49.05669946408082</v>
       </c>
       <c r="H45" t="n">
-        <v>237.8579541117109</v>
+        <v>45.12</v>
       </c>
       <c r="I45" t="n">
-        <v>44.72</v>
+        <v>45.12</v>
       </c>
       <c r="J45" t="n">
-        <v>239.0912041375631</v>
+        <v>239.4912041375631</v>
       </c>
       <c r="K45" t="n">
-        <v>548.633930609305</v>
+        <v>549.033930609305</v>
       </c>
       <c r="L45" t="n">
-        <v>981.8096988082788</v>
+        <v>982.2096988082787</v>
       </c>
       <c r="M45" t="n">
-        <v>1256.732740551138</v>
+        <v>1257.132740551138</v>
       </c>
       <c r="N45" t="n">
-        <v>1583.85362421531</v>
+        <v>1584.25362421531</v>
       </c>
       <c r="O45" t="n">
-        <v>1981.150683832657</v>
+        <v>2000.622354200916</v>
       </c>
       <c r="P45" t="n">
-        <v>2236.000000000276</v>
+        <v>2255.471670368536</v>
       </c>
       <c r="Q45" t="n">
-        <v>2236.000000000276</v>
+        <v>2255.471670368536</v>
       </c>
       <c r="R45" t="n">
-        <v>1730.41183044632</v>
+        <v>2074.125925057003</v>
       </c>
       <c r="S45" t="n">
-        <v>1273.259800750791</v>
+        <v>1941.216319603899</v>
       </c>
       <c r="T45" t="n">
-        <v>1191.115021705084</v>
+        <v>1859.071540558192</v>
       </c>
       <c r="U45" t="n">
-        <v>1111.15458588862</v>
+        <v>1779.111104741727</v>
       </c>
       <c r="V45" t="n">
-        <v>1016.699366503246</v>
+        <v>1684.655885356353</v>
       </c>
       <c r="W45" t="n">
-        <v>904.2012423519037</v>
+        <v>1247.915336962587</v>
       </c>
       <c r="X45" t="n">
-        <v>804.3398893767647</v>
+        <v>1148.053983987448</v>
       </c>
       <c r="Y45" t="n">
-        <v>725.1566643604674</v>
+        <v>1068.870758971151</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>668.386941496294</v>
+        <v>679.8904483778066</v>
       </c>
       <c r="C46" t="n">
-        <v>716.1789473147297</v>
+        <v>727.6824541962424</v>
       </c>
       <c r="D46" t="n">
-        <v>751.2880914397298</v>
+        <v>762.7915983212424</v>
       </c>
       <c r="E46" t="n">
-        <v>790.9069956511428</v>
+        <v>802.4105025326554</v>
       </c>
       <c r="F46" t="n">
-        <v>837.0579682430782</v>
+        <v>848.5614751245909</v>
       </c>
       <c r="G46" t="n">
-        <v>912.8793701955373</v>
+        <v>924.3828770770499</v>
       </c>
       <c r="H46" t="n">
-        <v>1009.741316010673</v>
+        <v>1021.244822892185</v>
       </c>
       <c r="I46" t="n">
-        <v>1171.454719536919</v>
+        <v>1182.958226418432</v>
       </c>
       <c r="J46" t="n">
-        <v>1498.504370025436</v>
+        <v>1510.007876906949</v>
       </c>
       <c r="K46" t="n">
-        <v>1603.253394126239</v>
+        <v>1603.653394126239</v>
       </c>
       <c r="L46" t="n">
-        <v>1594.452180057279</v>
+        <v>1594.852180057278</v>
       </c>
       <c r="M46" t="n">
-        <v>1492.738679551308</v>
+        <v>1493.138679551308</v>
       </c>
       <c r="N46" t="n">
-        <v>1337.584852898339</v>
+        <v>1337.984852898339</v>
       </c>
       <c r="O46" t="n">
-        <v>1105.023511470621</v>
+        <v>1105.423511470621</v>
       </c>
       <c r="P46" t="n">
-        <v>811.9796012698439</v>
+        <v>812.3796012698439</v>
       </c>
       <c r="Q46" t="n">
-        <v>456.4348877086338</v>
+        <v>456.8348877086338</v>
       </c>
       <c r="R46" t="n">
-        <v>75.40111047978445</v>
+        <v>75.80111047978446</v>
       </c>
       <c r="S46" t="n">
-        <v>44.72</v>
+        <v>45.12</v>
       </c>
       <c r="T46" t="n">
-        <v>146.1519263756528</v>
+        <v>157.6554332571655</v>
       </c>
       <c r="U46" t="n">
-        <v>314.5272009811526</v>
+        <v>326.0307078626653</v>
       </c>
       <c r="V46" t="n">
-        <v>435.1385938670986</v>
+        <v>446.6421007486113</v>
       </c>
       <c r="W46" t="n">
-        <v>528.819512126776</v>
+        <v>540.3230190082886</v>
       </c>
       <c r="X46" t="n">
-        <v>601.6403031509695</v>
+        <v>613.1438100324822</v>
       </c>
       <c r="Y46" t="n">
-        <v>634.8396038300018</v>
+        <v>646.3431107115144</v>
       </c>
     </row>
   </sheetData>
@@ -7964,7 +7964,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>373.8993027275024</v>
+        <v>0.2405037325275146</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -7973,19 +7973,19 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>471.5549969890509</v>
+        <v>655.6021670241489</v>
       </c>
       <c r="N2" t="n">
-        <v>403.3653500296342</v>
+        <v>778.0826666125488</v>
       </c>
       <c r="O2" t="n">
-        <v>374.4816735941929</v>
+        <v>375.1590153027356</v>
       </c>
       <c r="P2" t="n">
-        <v>314.7432258698271</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>368.9819249751683</v>
+        <v>502.5418702571336</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,28 +8201,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>246.8601159786807</v>
+        <v>373.8993027275024</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>308.6565929648241</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>845.554996989051</v>
+        <v>471.5549969890509</v>
       </c>
       <c r="N5" t="n">
-        <v>777.3653500296342</v>
+        <v>403.3653500296342</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4816735941929551</v>
+        <v>241.3558539403683</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>314.7432258698271</v>
       </c>
       <c r="Q5" t="n">
-        <v>128.1077446289929</v>
+        <v>502.1077446289929</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,10 +8438,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>181.5167089435048</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -8675,19 +8675,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>470.0198492462312</v>
+        <v>469.0198492462312</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>946.1990623156843</v>
+        <v>514.4530142644802</v>
       </c>
       <c r="N11" t="n">
-        <v>822.6797973356179</v>
+        <v>226.1881540497347</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8696,7 +8696,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>20.87871447823917</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8921,19 +8921,19 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>946.1990623156843</v>
+        <v>945.1990623156856</v>
       </c>
       <c r="N14" t="n">
-        <v>250.7726448352604</v>
+        <v>874.1881540497361</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>446.9536429552543</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>615.8520732695737</v>
+        <v>436.4306110507551</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,7 +9149,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -9158,19 +9158,19 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>321.7835531012099</v>
+        <v>945.1990623156856</v>
       </c>
       <c r="N17" t="n">
-        <v>875.1881540497347</v>
+        <v>859.4353140360948</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>446.9536429552543</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>20.87871447823917</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,7 +9386,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -9395,10 +9395,10 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>946.1990623156843</v>
+        <v>945.1990623156856</v>
       </c>
       <c r="N20" t="n">
-        <v>697.7262877905147</v>
+        <v>264.4619552447606</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -9623,7 +9623,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -9632,10 +9632,10 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>946.1990623156843</v>
+        <v>945.1990623156843</v>
       </c>
       <c r="N23" t="n">
-        <v>875.1881540497347</v>
+        <v>264.461955244762</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>438.3902070103535</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,16 +9860,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>419.4710884917101</v>
       </c>
       <c r="M26" t="n">
-        <v>936.3654142212374</v>
+        <v>947.1990623156843</v>
       </c>
       <c r="N26" t="n">
         <v>876.1881540497347</v>
@@ -10097,16 +10097,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>419.4710884917101</v>
       </c>
       <c r="M29" t="n">
-        <v>936.3654142212374</v>
+        <v>947.1990623156843</v>
       </c>
       <c r="N29" t="n">
         <v>876.1881540497347</v>
@@ -10334,7 +10334,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -10343,19 +10343,19 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>297.1990623156842</v>
+        <v>771.69679201606</v>
       </c>
       <c r="N32" t="n">
         <v>876.1881540497347</v>
       </c>
       <c r="O32" t="n">
-        <v>191.2127089502992</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>447.9536429552543</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>20.87871447823917</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10571,7 +10571,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -10580,10 +10580,10 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>856.1990623156929</v>
+        <v>861.1990623156843</v>
       </c>
       <c r="N35" t="n">
-        <v>596.031273632047</v>
+        <v>790.1881540497347</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>20.87871447823917</v>
+        <v>271.824550444697</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10659,7 +10659,7 @@
         <v>388.0893364597981</v>
       </c>
       <c r="M36" t="n">
-        <v>452.4305069265358</v>
+        <v>471.6948204301074</v>
       </c>
       <c r="N36" t="n">
         <v>485.4085271713503</v>
@@ -10808,19 +10808,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>380.0198492462312</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>336.9592964824121</v>
+        <v>341.959296482412</v>
       </c>
       <c r="M38" t="n">
-        <v>509.0630361693622</v>
+        <v>770.18560179973</v>
       </c>
       <c r="N38" t="n">
-        <v>226.1881540497347</v>
+        <v>790.1881540497347</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -10896,7 +10896,7 @@
         <v>388.0893364597981</v>
       </c>
       <c r="M39" t="n">
-        <v>452.4305069265358</v>
+        <v>471.6948204301074</v>
       </c>
       <c r="N39" t="n">
         <v>485.4085271713503</v>
@@ -11054,10 +11054,10 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>538.3469184840861</v>
+        <v>861.1990623156843</v>
       </c>
       <c r="N41" t="n">
-        <v>785.1881540497727</v>
+        <v>790.1881540497347</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>579.8787144782771</v>
+        <v>271.824550444697</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11130,7 +11130,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L42" t="n">
-        <v>368.8250229562266</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M42" t="n">
         <v>471.6948204301074</v>
@@ -11291,10 +11291,10 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>856.1990623157511</v>
+        <v>861.1990623156843</v>
       </c>
       <c r="N44" t="n">
-        <v>785.1881540498018</v>
+        <v>477.1339900161923</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>262.0265706468625</v>
+        <v>584.8787144782391</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -11376,7 +11376,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O45" t="n">
-        <v>363.4174852976117</v>
+        <v>382.6817988009037</v>
       </c>
       <c r="P45" t="n">
         <v>219.1507118405495</v>
@@ -23241,7 +23241,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2.491901076897236</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -23475,7 +23475,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2.491901076897254</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -23715,7 +23715,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2.491901076884631</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -23952,7 +23952,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>2.491901076883735</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -24189,7 +24189,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>2.491901076897236</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -25134,7 +25134,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>11.88310107689719</v>
+        <v>6.479101076896939</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -25368,7 +25368,7 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>11.8831010768972</v>
+        <v>6.479101076896534</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -25596,13 +25596,13 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>20.70411980934601</v>
+        <v>7.275985942327111</v>
       </c>
       <c r="D41" t="n">
-        <v>89.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>83.36328960686865</v>
       </c>
       <c r="F41" t="n">
         <v>83.88962870801186</v>
@@ -25611,7 +25611,7 @@
         <v>81.35033711113681</v>
       </c>
       <c r="H41" t="n">
-        <v>72.59985970855254</v>
+        <v>72.59985970855251</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25833,22 +25833,22 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>128.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>7.275985942327125</v>
       </c>
       <c r="E44" t="n">
-        <v>77.62316910165819</v>
+        <v>83.36328960686865</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>83.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>81.35033711113681</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>72.59985970855251</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25881,7 +25881,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>141.7853537319712</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>979565.8926841225</v>
+        <v>979675.7346841225</v>
       </c>
     </row>
     <row r="3">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3623129.37004924</v>
+        <v>3622895.96616972</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4504693.298282056</v>
+        <v>4504321.045674531</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5386257.226514872</v>
+        <v>5385746.125179344</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6267821.154747685</v>
+        <v>6267171.204684152</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7149385.082980499</v>
+        <v>7148596.284188961</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8031043.566364826</v>
+        <v>8030349.322724804</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8912607.49459764</v>
+        <v>8911913.250957618</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9794171.422830459</v>
+        <v>9793477.179190436</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10666223.66381563</v>
+        <v>10666548.34888095</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11547125.46565645</v>
+        <v>11547751.26160177</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12409305.34749727</v>
+        <v>12411012.33432258</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13271485.22933811</v>
+        <v>13274273.4070434</v>
       </c>
     </row>
   </sheetData>
@@ -26269,49 +26269,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1322345.892349225</v>
+        <v>1322345.892349224</v>
       </c>
       <c r="C2" t="n">
         <v>1322345.892349224</v>
       </c>
       <c r="D2" t="n">
-        <v>1322345.892349225</v>
+        <v>1322345.892349224</v>
       </c>
       <c r="E2" t="n">
-        <v>1322345.892349225</v>
+        <v>1322137.619257217</v>
       </c>
       <c r="F2" t="n">
-        <v>1322345.892349225</v>
+        <v>1322137.619257218</v>
       </c>
       <c r="G2" t="n">
+        <v>1322137.619257218</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1322137.619257218</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1322137.619257217</v>
+      </c>
+      <c r="J2" t="n">
         <v>1322345.892349224</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1322345.892349224</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1322345.892349224</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1322345.892349225</v>
       </c>
       <c r="K2" t="n">
         <v>1322345.892349225</v>
       </c>
       <c r="L2" t="n">
-        <v>1322345.892349225</v>
+        <v>1322345.892349224</v>
       </c>
       <c r="M2" t="n">
-        <v>1321352.702761217</v>
+        <v>1321804.369081218</v>
       </c>
       <c r="N2" t="n">
-        <v>1321352.702761217</v>
+        <v>1321804.369081218</v>
       </c>
       <c r="O2" t="n">
-        <v>1293269.822761217</v>
+        <v>1294891.609081217</v>
       </c>
       <c r="P2" t="n">
-        <v>1293269.822761239</v>
+        <v>1294891.609081217</v>
       </c>
     </row>
     <row r="3">
@@ -26321,16 +26321,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>232073</v>
+        <v>231098</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>975</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>594425</v>
+        <v>594073</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26345,7 +26345,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>388800</v>
+        <v>389152</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26354,13 +26354,13 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>83968</v>
+        <v>84576</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>237600</v>
+        <v>238400</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>602166.8573620638</v>
+        <v>602219.8615549037</v>
       </c>
       <c r="C4" t="n">
-        <v>600158.4933044576</v>
+        <v>599959.4017938485</v>
       </c>
       <c r="D4" t="n">
-        <v>598147.4047756541</v>
+        <v>597948.3132650448</v>
       </c>
       <c r="E4" t="n">
-        <v>513253.1653847605</v>
+        <v>513021.1273989228</v>
       </c>
       <c r="F4" t="n">
-        <v>511570.4197316588</v>
+        <v>511338.1266634626</v>
       </c>
       <c r="G4" t="n">
-        <v>509885.3519526902</v>
+        <v>509652.8034501319</v>
       </c>
       <c r="H4" t="n">
-        <v>508197.9453958012</v>
+        <v>507965.1411043521</v>
       </c>
       <c r="I4" t="n">
-        <v>506508.1831919707</v>
+        <v>506275.1227545446</v>
       </c>
       <c r="J4" t="n">
-        <v>504742.7776510159</v>
+        <v>504545.7862134472</v>
       </c>
       <c r="K4" t="n">
-        <v>503048.9703867821</v>
+        <v>502851.9789492135</v>
       </c>
       <c r="L4" t="n">
-        <v>501352.7565448463</v>
+        <v>501155.7651072776</v>
       </c>
       <c r="M4" t="n">
-        <v>505738.3237785161</v>
+        <v>505255.6137435236</v>
       </c>
       <c r="N4" t="n">
-        <v>503972.1894956147</v>
+        <v>503493.9398297629</v>
       </c>
       <c r="O4" t="n">
-        <v>487738.9374419111</v>
+        <v>487867.9540901374</v>
       </c>
       <c r="P4" t="n">
-        <v>486030.0621167537</v>
+        <v>486160.9521894817</v>
       </c>
     </row>
     <row r="5">
@@ -26425,7 +26425,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58612.2</v>
+        <v>58590.39999999999</v>
       </c>
       <c r="C5" t="n">
         <v>58612.2</v>
@@ -26434,19 +26434,19 @@
         <v>58612.2</v>
       </c>
       <c r="E5" t="n">
-        <v>74075.349</v>
+        <v>74014.549</v>
       </c>
       <c r="F5" t="n">
-        <v>74075.349</v>
+        <v>74014.549</v>
       </c>
       <c r="G5" t="n">
-        <v>74075.349</v>
+        <v>74014.549</v>
       </c>
       <c r="H5" t="n">
-        <v>74075.349</v>
+        <v>74014.549</v>
       </c>
       <c r="I5" t="n">
-        <v>74075.349</v>
+        <v>74014.549</v>
       </c>
       <c r="J5" t="n">
         <v>74136.149</v>
@@ -26458,16 +26458,16 @@
         <v>74136.149</v>
       </c>
       <c r="M5" t="n">
-        <v>70621.005</v>
+        <v>70840.936</v>
       </c>
       <c r="N5" t="n">
-        <v>70621.005</v>
+        <v>70840.936</v>
       </c>
       <c r="O5" t="n">
-        <v>68603.349</v>
+        <v>68907.349</v>
       </c>
       <c r="P5" t="n">
-        <v>68603.349</v>
+        <v>68907.349</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>429493.8349871609</v>
+        <v>430437.6307943206</v>
       </c>
       <c r="C6" t="n">
-        <v>663575.1990447663</v>
+        <v>662799.2905553754</v>
       </c>
       <c r="D6" t="n">
-        <v>665586.2875735705</v>
+        <v>665785.3790841795</v>
       </c>
       <c r="E6" t="n">
-        <v>140592.3779644642</v>
+        <v>141028.942858294</v>
       </c>
       <c r="F6" t="n">
-        <v>736700.1236175657</v>
+        <v>736784.9435937549</v>
       </c>
       <c r="G6" t="n">
-        <v>738385.1913965341</v>
+        <v>738470.2668070861</v>
       </c>
       <c r="H6" t="n">
-        <v>740072.5979534228</v>
+        <v>740157.9291528662</v>
       </c>
       <c r="I6" t="n">
-        <v>741762.3601572531</v>
+        <v>741847.9475026727</v>
       </c>
       <c r="J6" t="n">
-        <v>354666.9656982089</v>
+        <v>354511.9571357771</v>
       </c>
       <c r="K6" t="n">
-        <v>745160.7729624424</v>
+        <v>745357.7644000113</v>
       </c>
       <c r="L6" t="n">
-        <v>746856.9868043785</v>
+        <v>747053.9782419465</v>
       </c>
       <c r="M6" t="n">
-        <v>661025.3739827004</v>
+        <v>661131.8193376947</v>
       </c>
       <c r="N6" t="n">
-        <v>746759.5082656023</v>
+        <v>747469.4932514554</v>
       </c>
       <c r="O6" t="n">
-        <v>499327.5363193058</v>
+        <v>499716.3059910797</v>
       </c>
       <c r="P6" t="n">
-        <v>738636.4116444857</v>
+        <v>739823.3078917356</v>
       </c>
     </row>
   </sheetData>
@@ -26788,10 +26788,10 @@
         <v>321</v>
       </c>
       <c r="M2" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N2" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="O2" t="n">
         <v>321</v>
@@ -26807,7 +26807,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C3" t="n">
         <v>103</v>
@@ -26868,19 +26868,19 @@
         <v>374</v>
       </c>
       <c r="E4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="I4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="J4" t="n">
         <v>650</v>
@@ -26892,16 +26892,16 @@
         <v>650</v>
       </c>
       <c r="M4" t="n">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="N4" t="n">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="O4" t="n">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="P4" t="n">
-        <v>559</v>
+        <v>564</v>
       </c>
     </row>
   </sheetData>
@@ -26978,13 +26978,13 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E2" t="n">
         <v>321</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G2" t="n">
         <v>-0</v>
@@ -26999,19 +26999,19 @@
         <v>321</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L2" t="n">
         <v>-0</v>
       </c>
       <c r="M2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O2" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P2" t="n">
         <v>-0</v>
@@ -27024,19 +27024,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>247</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>-0</v>
@@ -27085,7 +27085,7 @@
         <v>-0</v>
       </c>
       <c r="E4" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F4" t="n">
         <v>-0</v>
@@ -27100,16 +27100,16 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L4" t="n">
         <v>-0</v>
       </c>
       <c r="M4" t="n">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="N4" t="n">
         <v>-0</v>
@@ -27326,7 +27326,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>134.1177124465037</v>
+        <v>134.2726973711268</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>222.9148456338345</v>
+        <v>223.3220918649904</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27521,19 +27521,19 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>325.517988705216</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>330.0491815260438</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27560,7 +27560,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>243.1511452982488</v>
+        <v>400</v>
       </c>
       <c r="S3" t="n">
         <v>400</v>
@@ -27578,10 +27578,10 @@
         <v>400</v>
       </c>
       <c r="X3" t="n">
-        <v>400</v>
+        <v>45.86273944538755</v>
       </c>
       <c r="Y3" t="n">
-        <v>399.3913927661343</v>
+        <v>43.44166921037822</v>
       </c>
     </row>
     <row r="4">
@@ -27591,37 +27591,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F4" t="n">
-        <v>327.3892915919513</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
-        <v>400</v>
+        <v>244.8599384153005</v>
       </c>
       <c r="H4" t="n">
-        <v>400</v>
+        <v>227.1357818393235</v>
       </c>
       <c r="I4" t="n">
-        <v>400</v>
+        <v>175.881563426005</v>
       </c>
       <c r="J4" t="n">
-        <v>22.13729309820286</v>
+        <v>396.2647849014816</v>
       </c>
       <c r="K4" t="n">
         <v>400</v>
       </c>
       <c r="L4" t="n">
-        <v>395.9334970102382</v>
+        <v>400</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -27642,22 +27642,22 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>359.1365780635112</v>
+        <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>209.2309599488807</v>
+        <v>400</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9482601269169</v>
+        <v>400</v>
       </c>
       <c r="V4" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W4" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X4" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
         <v>287.4653528494624</v>
@@ -27691,7 +27691,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>132.1643059857122</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27721,7 +27721,7 @@
         <v>224.8682520946261</v>
       </c>
       <c r="S5" t="n">
-        <v>400</v>
+        <v>398.0465935392085</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
@@ -27755,22 +27755,22 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>171.9171363915497</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>325.517988705216</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27794,10 +27794,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R6" t="n">
-        <v>159.5184388018133</v>
+        <v>400</v>
       </c>
       <c r="S6" t="n">
         <v>400</v>
@@ -27812,7 +27812,7 @@
         <v>400</v>
       </c>
       <c r="W6" t="n">
-        <v>140.9606092745227</v>
+        <v>400</v>
       </c>
       <c r="X6" t="n">
         <v>400</v>
@@ -27828,16 +27828,16 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>287.1138003370787</v>
+      </c>
+      <c r="C7" t="n">
+        <v>272.7252466480447</v>
+      </c>
+      <c r="D7" t="n">
+        <v>323.8629409197806</v>
+      </c>
+      <c r="E7" t="n">
         <v>400</v>
-      </c>
-      <c r="C7" t="n">
-        <v>400</v>
-      </c>
-      <c r="D7" t="n">
-        <v>285.5362180555555</v>
-      </c>
-      <c r="E7" t="n">
-        <v>280.9809048369565</v>
       </c>
       <c r="F7" t="n">
         <v>274.3828559677419</v>
@@ -27852,13 +27852,13 @@
         <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>117.3106534979975</v>
+        <v>22.13729309820286</v>
       </c>
       <c r="K7" t="n">
-        <v>266.941429538848</v>
+        <v>400</v>
       </c>
       <c r="L7" t="n">
-        <v>395.9334970102382</v>
+        <v>400</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27879,7 +27879,7 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>359.1365780635112</v>
+        <v>400</v>
       </c>
       <c r="T7" t="n">
         <v>400</v>
@@ -27955,10 +27955,10 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>222.9148456338345</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S8" t="n">
-        <v>400</v>
+        <v>398.0465935392085</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
@@ -27992,13 +27992,13 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
         <v>325.517988705216</v>
@@ -28007,7 +28007,7 @@
         <v>330.0284079411381</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28031,13 +28031,13 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
       </c>
       <c r="S9" t="n">
-        <v>252.7589796949875</v>
+        <v>400</v>
       </c>
       <c r="T9" t="n">
         <v>400</v>
@@ -28046,10 +28046,10 @@
         <v>400</v>
       </c>
       <c r="V9" t="n">
-        <v>400</v>
+        <v>40.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>400</v>
+        <v>266.2522381569365</v>
       </c>
       <c r="X9" t="n">
         <v>400</v>
@@ -28065,13 +28065,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C10" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E10" t="n">
         <v>400</v>
@@ -28089,10 +28089,10 @@
         <v>400</v>
       </c>
       <c r="J10" t="n">
-        <v>259.2213947232248</v>
+        <v>22.13729309820286</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>266.941429538848</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28116,7 +28116,7 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>400</v>
+        <v>359.1365780635112</v>
       </c>
       <c r="T10" t="n">
         <v>209.2309599488807</v>
@@ -28134,7 +28134,7 @@
         <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>287.4653528494624</v>
+        <v>343.8467119128038</v>
       </c>
     </row>
     <row r="11">
@@ -28195,7 +28195,7 @@
         <v>162.4939254614603</v>
       </c>
       <c r="S11" t="n">
-        <v>319.6111010768973</v>
+        <v>321</v>
       </c>
       <c r="T11" t="n">
         <v>321</v>
@@ -28235,16 +28235,16 @@
         <v>321</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="H12" t="n">
-        <v>319.4798568942804</v>
+        <v>321</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>75.46100877721307</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -28268,13 +28268,13 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>76.98115188293241</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>321</v>
@@ -28359,10 +28359,10 @@
         <v>321</v>
       </c>
       <c r="U13" t="n">
-        <v>309.7843364833203</v>
+        <v>321</v>
       </c>
       <c r="V13" t="n">
-        <v>321</v>
+        <v>309.7843364833204</v>
       </c>
       <c r="W13" t="n">
         <v>321</v>
@@ -28432,7 +28432,7 @@
         <v>162.4939254614603</v>
       </c>
       <c r="S14" t="n">
-        <v>319.6111010768973</v>
+        <v>321</v>
       </c>
       <c r="T14" t="n">
         <v>321</v>
@@ -28460,25 +28460,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>128.2732823236869</v>
+        <v>321</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>321</v>
+        <v>128.2732823236874</v>
       </c>
       <c r="I15" t="n">
         <v>191.2065745705938</v>
@@ -28560,7 +28560,7 @@
         <v>321</v>
       </c>
       <c r="I16" t="n">
-        <v>321</v>
+        <v>309.7843364833205</v>
       </c>
       <c r="J16" t="n">
         <v>321</v>
@@ -28593,7 +28593,7 @@
         <v>321</v>
       </c>
       <c r="T16" t="n">
-        <v>309.7843364833203</v>
+        <v>321</v>
       </c>
       <c r="U16" t="n">
         <v>321</v>
@@ -28666,7 +28666,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>161.1050265383575</v>
+        <v>162.4939254614724</v>
       </c>
       <c r="S17" t="n">
         <v>321</v>
@@ -28703,22 +28703,22 @@
         <v>321</v>
       </c>
       <c r="D18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>321</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>128.273282323687</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="H18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>191.2065745705938</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -28745,7 +28745,7 @@
         <v>76.98115188293241</v>
       </c>
       <c r="R18" t="n">
-        <v>319.4798568942803</v>
+        <v>321</v>
       </c>
       <c r="S18" t="n">
         <v>321</v>
@@ -28757,13 +28757,13 @@
         <v>321</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W18" t="n">
         <v>321</v>
       </c>
       <c r="X18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>321</v>
@@ -28785,52 +28785,52 @@
         <v>321</v>
       </c>
       <c r="E19" t="n">
+        <v>321</v>
+      </c>
+      <c r="F19" t="n">
+        <v>321</v>
+      </c>
+      <c r="G19" t="n">
+        <v>321</v>
+      </c>
+      <c r="H19" t="n">
+        <v>321</v>
+      </c>
+      <c r="I19" t="n">
+        <v>321</v>
+      </c>
+      <c r="J19" t="n">
+        <v>321</v>
+      </c>
+      <c r="K19" t="n">
+        <v>321</v>
+      </c>
+      <c r="L19" t="n">
+        <v>321</v>
+      </c>
+      <c r="M19" t="n">
+        <v>321</v>
+      </c>
+      <c r="N19" t="n">
+        <v>321</v>
+      </c>
+      <c r="O19" t="n">
+        <v>321</v>
+      </c>
+      <c r="P19" t="n">
+        <v>321</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>321</v>
+      </c>
+      <c r="R19" t="n">
+        <v>321</v>
+      </c>
+      <c r="S19" t="n">
+        <v>321</v>
+      </c>
+      <c r="T19" t="n">
         <v>309.7843364833204</v>
-      </c>
-      <c r="F19" t="n">
-        <v>321</v>
-      </c>
-      <c r="G19" t="n">
-        <v>321</v>
-      </c>
-      <c r="H19" t="n">
-        <v>321</v>
-      </c>
-      <c r="I19" t="n">
-        <v>321</v>
-      </c>
-      <c r="J19" t="n">
-        <v>321</v>
-      </c>
-      <c r="K19" t="n">
-        <v>321</v>
-      </c>
-      <c r="L19" t="n">
-        <v>321</v>
-      </c>
-      <c r="M19" t="n">
-        <v>321</v>
-      </c>
-      <c r="N19" t="n">
-        <v>321</v>
-      </c>
-      <c r="O19" t="n">
-        <v>321</v>
-      </c>
-      <c r="P19" t="n">
-        <v>321</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>321</v>
-      </c>
-      <c r="R19" t="n">
-        <v>321</v>
-      </c>
-      <c r="S19" t="n">
-        <v>321</v>
-      </c>
-      <c r="T19" t="n">
-        <v>321</v>
       </c>
       <c r="U19" t="n">
         <v>321</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>161.1050265383575</v>
+        <v>162.4939254614733</v>
       </c>
       <c r="S20" t="n">
         <v>321</v>
@@ -28934,7 +28934,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>321</v>
+        <v>128.2732823236873</v>
       </c>
       <c r="C21" t="n">
         <v>321</v>
@@ -28991,7 +28991,7 @@
         <v>321</v>
       </c>
       <c r="U21" t="n">
-        <v>128.2732823236869</v>
+        <v>321</v>
       </c>
       <c r="V21" t="n">
         <v>321</v>
@@ -29143,7 +29143,7 @@
         <v>162.4939254614603</v>
       </c>
       <c r="S23" t="n">
-        <v>319.6111010768973</v>
+        <v>321</v>
       </c>
       <c r="T23" t="n">
         <v>321</v>
@@ -29216,28 +29216,28 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>76.98115188293241</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="T24" t="n">
         <v>321</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>128.2732823236871</v>
       </c>
       <c r="V24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>205.2544342066187</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
         <v>321</v>
@@ -29274,10 +29274,10 @@
         <v>321</v>
       </c>
       <c r="J25" t="n">
-        <v>321</v>
+        <v>309.7843364833205</v>
       </c>
       <c r="K25" t="n">
-        <v>309.7843364833207</v>
+        <v>321</v>
       </c>
       <c r="L25" t="n">
         <v>321</v>
@@ -29350,7 +29350,7 @@
         <v>321</v>
       </c>
       <c r="I26" t="n">
-        <v>95.83643606459415</v>
+        <v>90.56673714149139</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29377,7 +29377,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>157.2242265383575</v>
+        <v>162.4939254614603</v>
       </c>
       <c r="S26" t="n">
         <v>321</v>
@@ -29408,10 +29408,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>321</v>
+        <v>128.2732823236869</v>
       </c>
       <c r="D27" t="n">
         <v>321</v>
@@ -29420,7 +29420,7 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G27" t="n">
         <v>321</v>
@@ -29429,7 +29429,7 @@
         <v>321</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>191.2065745705938</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -29456,10 +29456,10 @@
         <v>76.98115188293241</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="S27" t="n">
-        <v>319.4798568942804</v>
+        <v>321</v>
       </c>
       <c r="T27" t="n">
         <v>321</v>
@@ -29474,7 +29474,7 @@
         <v>321</v>
       </c>
       <c r="X27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
         <v>321</v>
@@ -29499,7 +29499,7 @@
         <v>321</v>
       </c>
       <c r="F28" t="n">
-        <v>309.7843364833201</v>
+        <v>321</v>
       </c>
       <c r="G28" t="n">
         <v>321</v>
@@ -29541,7 +29541,7 @@
         <v>321</v>
       </c>
       <c r="T28" t="n">
-        <v>321</v>
+        <v>309.7843364833203</v>
       </c>
       <c r="U28" t="n">
         <v>321</v>
@@ -29614,10 +29614,10 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>157.2242265383575</v>
+        <v>162.4939254614603</v>
       </c>
       <c r="S29" t="n">
-        <v>321</v>
+        <v>315.7303010768973</v>
       </c>
       <c r="T29" t="n">
         <v>321</v>
@@ -29645,19 +29645,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C30" t="n">
-        <v>205.2544342066188</v>
+        <v>321</v>
       </c>
       <c r="D30" t="n">
-        <v>321</v>
+        <v>128.2732823236869</v>
       </c>
       <c r="E30" t="n">
         <v>321</v>
       </c>
       <c r="F30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>321</v>
@@ -29690,10 +29690,10 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>76.98115188293241</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="S30" t="n">
         <v>321</v>
@@ -29702,13 +29702,13 @@
         <v>321</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="V30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>321</v>
@@ -29727,13 +29727,13 @@
         <v>321</v>
       </c>
       <c r="C31" t="n">
+        <v>321</v>
+      </c>
+      <c r="D31" t="n">
+        <v>321</v>
+      </c>
+      <c r="E31" t="n">
         <v>309.7843364833202</v>
-      </c>
-      <c r="D31" t="n">
-        <v>321</v>
-      </c>
-      <c r="E31" t="n">
-        <v>321</v>
       </c>
       <c r="F31" t="n">
         <v>321</v>
@@ -29824,7 +29824,7 @@
         <v>321</v>
       </c>
       <c r="I32" t="n">
-        <v>90.56673714149142</v>
+        <v>95.83643606459415</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>162.4939254614603</v>
+        <v>157.2242265383575</v>
       </c>
       <c r="S32" t="n">
         <v>321</v>
@@ -29888,10 +29888,10 @@
         <v>321</v>
       </c>
       <c r="D33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>321</v>
@@ -29930,25 +29930,25 @@
         <v>76.98115188293241</v>
       </c>
       <c r="R33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>321</v>
+        <v>128.2732823236865</v>
       </c>
       <c r="T33" t="n">
         <v>321</v>
       </c>
       <c r="U33" t="n">
-        <v>128.2732823236869</v>
+        <v>321</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y33" t="n">
         <v>321</v>
@@ -29973,7 +29973,7 @@
         <v>321</v>
       </c>
       <c r="F34" t="n">
-        <v>309.7843364833201</v>
+        <v>321</v>
       </c>
       <c r="G34" t="n">
         <v>321</v>
@@ -29985,7 +29985,7 @@
         <v>321</v>
       </c>
       <c r="J34" t="n">
-        <v>321</v>
+        <v>309.7843364833203</v>
       </c>
       <c r="K34" t="n">
         <v>321</v>
@@ -30040,25 +30040,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C35" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D35" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E35" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F35" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G35" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H35" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I35" t="n">
         <v>95.83643606459415</v>
@@ -30091,25 +30091,25 @@
         <v>162.4939254614603</v>
       </c>
       <c r="S35" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="T35" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="U35" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="V35" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="W35" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="X35" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Y35" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="36">
@@ -30119,22 +30119,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>345</v>
+        <v>301.9460946468293</v>
       </c>
       <c r="C36" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>344</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>324.9867056863481</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -30167,28 +30167,28 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>325.1486821851209</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="U36" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="V36" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="W36" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="X36" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Y36" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="37">
@@ -30198,76 +30198,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C37" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D37" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E37" t="n">
-        <v>280.9809048369565</v>
+        <v>344</v>
       </c>
       <c r="F37" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G37" t="n">
-        <v>334.2829999021351</v>
+        <v>344</v>
       </c>
       <c r="H37" t="n">
-        <v>345</v>
+        <v>223.1596506917826</v>
       </c>
       <c r="I37" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="J37" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="L37" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="M37" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N37" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="O37" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="P37" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Q37" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="R37" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="S37" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="T37" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="U37" t="n">
-        <v>150.9239650449497</v>
+        <v>344</v>
       </c>
       <c r="V37" t="n">
-        <v>199.1703102162162</v>
+        <v>242.1788203508965</v>
       </c>
       <c r="W37" t="n">
-        <v>226.3728098387097</v>
+        <v>344</v>
       </c>
       <c r="X37" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Y37" t="n">
-        <v>287.4653528494624</v>
+        <v>344</v>
       </c>
     </row>
     <row r="38">
@@ -30277,25 +30277,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C38" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D38" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E38" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F38" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G38" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H38" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I38" t="n">
         <v>95.83643606459415</v>
@@ -30328,25 +30328,25 @@
         <v>162.4939254614603</v>
       </c>
       <c r="S38" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="T38" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="U38" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="V38" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="W38" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="X38" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Y38" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="39">
@@ -30356,13 +30356,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C39" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D39" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E39" t="n">
         <v>342.6720972219126</v>
@@ -30371,10 +30371,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>324.9867056863481</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>324.89733246944</v>
       </c>
       <c r="I39" t="n">
         <v>191.2065745705938</v>
@@ -30401,31 +30401,31 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>76.98115188293241</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>235.8458964287475</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>345</v>
+        <v>340.0620564910412</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>344</v>
       </c>
       <c r="W39" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="40">
@@ -30435,76 +30435,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C40" t="n">
-        <v>345</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D40" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E40" t="n">
-        <v>280.9809048369565</v>
+        <v>344</v>
       </c>
       <c r="F40" t="n">
-        <v>274.3828559677419</v>
+        <v>344</v>
       </c>
       <c r="G40" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H40" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I40" t="n">
         <v>157.6531277512658</v>
       </c>
       <c r="J40" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="K40" t="n">
-        <v>215.192904948684</v>
+        <v>330.7487393040992</v>
       </c>
       <c r="L40" t="n">
-        <v>345</v>
+        <v>329.713201928271</v>
       </c>
       <c r="M40" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N40" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="O40" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="P40" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Q40" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="R40" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="S40" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="T40" t="n">
-        <v>345</v>
+        <v>207.3278451947823</v>
       </c>
       <c r="U40" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="V40" t="n">
-        <v>205.9865491837814</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W40" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="X40" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Y40" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="41">
@@ -30593,19 +30593,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C42" t="n">
         <v>321</v>
       </c>
       <c r="D42" t="n">
-        <v>147.1542359885374</v>
+        <v>321</v>
       </c>
       <c r="E42" t="n">
         <v>321</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G42" t="n">
         <v>321</v>
@@ -30641,7 +30641,7 @@
         <v>76.98115188293241</v>
       </c>
       <c r="R42" t="n">
-        <v>321</v>
+        <v>128.2732823236871</v>
       </c>
       <c r="S42" t="n">
         <v>321</v>
@@ -30653,13 +30653,13 @@
         <v>321</v>
       </c>
       <c r="V42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
         <v>321</v>
       </c>
       <c r="X42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
         <v>321</v>
@@ -30726,10 +30726,10 @@
         <v>321</v>
       </c>
       <c r="T43" t="n">
-        <v>309.7843364833205</v>
+        <v>321</v>
       </c>
       <c r="U43" t="n">
-        <v>321</v>
+        <v>309.7843364833204</v>
       </c>
       <c r="V43" t="n">
         <v>321</v>
@@ -30833,16 +30833,16 @@
         <v>321</v>
       </c>
       <c r="C45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
         <v>321</v>
       </c>
       <c r="E45" t="n">
-        <v>321</v>
+        <v>128.2732823236868</v>
       </c>
       <c r="F45" t="n">
-        <v>17.36081055885705</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>321</v>
@@ -30851,7 +30851,7 @@
         <v>321</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>191.2065745705938</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -30878,10 +30878,10 @@
         <v>76.98115188293241</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="T45" t="n">
         <v>321</v>
@@ -30893,7 +30893,7 @@
         <v>321</v>
       </c>
       <c r="W45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
         <v>321</v>
@@ -30936,7 +30936,7 @@
         <v>321</v>
       </c>
       <c r="K46" t="n">
-        <v>321</v>
+        <v>309.7843364833204</v>
       </c>
       <c r="L46" t="n">
         <v>321</v>
@@ -30963,7 +30963,7 @@
         <v>321</v>
       </c>
       <c r="T46" t="n">
-        <v>309.7843364833205</v>
+        <v>321</v>
       </c>
       <c r="U46" t="n">
         <v>321</v>
@@ -31091,49 +31091,49 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4140703517587936</v>
+        <v>0.4100502512562811</v>
       </c>
       <c r="H2" t="n">
-        <v>4.240597989949746</v>
+        <v>4.199427135678389</v>
       </c>
       <c r="I2" t="n">
-        <v>15.96344723618091</v>
+        <v>15.80846231155779</v>
       </c>
       <c r="J2" t="n">
-        <v>35.14370351758794</v>
+        <v>34.80250251256282</v>
       </c>
       <c r="K2" t="n">
-        <v>52.67130150753769</v>
+        <v>52.15992964824121</v>
       </c>
       <c r="L2" t="n">
-        <v>65.34340703517589</v>
+        <v>64.70900502512563</v>
       </c>
       <c r="M2" t="n">
-        <v>72.70713065326633</v>
+        <v>72.00123618090453</v>
       </c>
       <c r="N2" t="n">
-        <v>73.88360804020101</v>
+        <v>73.16629145728643</v>
       </c>
       <c r="O2" t="n">
-        <v>69.76619597989949</v>
+        <v>69.08885427135678</v>
       </c>
       <c r="P2" t="n">
-        <v>59.54383417085427</v>
+        <v>58.96573869346734</v>
       </c>
       <c r="Q2" t="n">
-        <v>44.71493969849246</v>
+        <v>44.28081407035176</v>
       </c>
       <c r="R2" t="n">
-        <v>26.01034673366835</v>
+        <v>25.75781909547739</v>
       </c>
       <c r="S2" t="n">
-        <v>9.435628140703519</v>
+        <v>9.344020100502515</v>
       </c>
       <c r="T2" t="n">
-        <v>1.81259296482412</v>
+        <v>1.794994974874371</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03312562814070349</v>
+        <v>0.03280402010050248</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -31170,49 +31170,49 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2215471698113208</v>
+        <v>0.2193962264150943</v>
       </c>
       <c r="H3" t="n">
-        <v>2.139679245283019</v>
+        <v>2.118905660377359</v>
       </c>
       <c r="I3" t="n">
-        <v>7.627830188679247</v>
+        <v>7.553773584905661</v>
       </c>
       <c r="J3" t="n">
-        <v>20.93134905660378</v>
+        <v>20.7281320754717</v>
       </c>
       <c r="K3" t="n">
-        <v>35.77500943396227</v>
+        <v>35.42767924528302</v>
       </c>
       <c r="L3" t="n">
-        <v>48.10391509433963</v>
+        <v>47.63688679245283</v>
       </c>
       <c r="M3" t="n">
-        <v>56.13499999999999</v>
+        <v>55.58999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>57.62072641509435</v>
+        <v>57.06130188679246</v>
       </c>
       <c r="O3" t="n">
-        <v>52.71170754716981</v>
+        <v>52.19994339622642</v>
       </c>
       <c r="P3" t="n">
-        <v>42.3057924528302</v>
+        <v>41.89505660377359</v>
       </c>
       <c r="Q3" t="n">
-        <v>28.28030188679246</v>
+        <v>28.00573584905661</v>
       </c>
       <c r="R3" t="n">
-        <v>13.75535849056604</v>
+        <v>13.62181132075472</v>
       </c>
       <c r="S3" t="n">
-        <v>4.115141509433959</v>
+        <v>4.07518867924528</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8929905660377355</v>
+        <v>0.8843207547169808</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01457547169811321</v>
+        <v>0.01443396226415095</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -31249,49 +31249,49 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1857377049180328</v>
+        <v>0.1839344262295082</v>
       </c>
       <c r="H4" t="n">
-        <v>1.651377049180329</v>
+        <v>1.635344262295083</v>
       </c>
       <c r="I4" t="n">
-        <v>5.585639344262296</v>
+        <v>5.531409836065575</v>
       </c>
       <c r="J4" t="n">
-        <v>13.13165573770492</v>
+        <v>13.00416393442623</v>
       </c>
       <c r="K4" t="n">
-        <v>21.57934426229507</v>
+        <v>21.36983606557376</v>
       </c>
       <c r="L4" t="n">
-        <v>27.61413114754098</v>
+        <v>27.34603278688525</v>
       </c>
       <c r="M4" t="n">
-        <v>29.11522950819672</v>
+        <v>28.83255737704917</v>
       </c>
       <c r="N4" t="n">
-        <v>28.42293442622952</v>
+        <v>28.1469836065574</v>
       </c>
       <c r="O4" t="n">
-        <v>26.25318032786886</v>
+        <v>25.99829508196722</v>
       </c>
       <c r="P4" t="n">
-        <v>22.46413114754097</v>
+        <v>22.24603278688523</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.553</v>
+        <v>15.402</v>
       </c>
       <c r="R4" t="n">
-        <v>8.351442622950817</v>
+        <v>8.270360655737703</v>
       </c>
       <c r="S4" t="n">
-        <v>3.236901639344261</v>
+        <v>3.205475409836064</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7936065573770489</v>
+        <v>0.785901639344262</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01013114754098362</v>
+        <v>0.01003278688524591</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -34743,28 +34743,28 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>52.1599296482412</v>
+      </c>
+      <c r="L2" t="n">
+        <v>64.70900502512562</v>
+      </c>
+      <c r="M2" t="n">
+        <v>183.3412755627362</v>
+      </c>
+      <c r="N2" t="n">
         <v>374</v>
-      </c>
-      <c r="K2" t="n">
-        <v>52.67130150753769</v>
-      </c>
-      <c r="L2" t="n">
-        <v>65.34340703517586</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>374</v>
       </c>
       <c r="P2" t="n">
+        <v>58.67867865278593</v>
+      </c>
+      <c r="Q2" t="n">
         <v>374</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>240.8741803461754</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34822,25 +34822,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>146.1399552942795</v>
+        <v>145.9367383131474</v>
       </c>
       <c r="K3" t="n">
-        <v>226.8788640747536</v>
+        <v>226.5315338860743</v>
       </c>
       <c r="L3" t="n">
-        <v>322.1952904430266</v>
+        <v>321.7282621411399</v>
       </c>
       <c r="M3" t="n">
-        <v>143.0850421645043</v>
+        <v>142.5400421645043</v>
       </c>
       <c r="N3" t="n">
-        <v>192.2472765237492</v>
+        <v>191.6878519954473</v>
       </c>
       <c r="O3" t="n">
-        <v>294.1687294499162</v>
+        <v>293.6569652989728</v>
       </c>
       <c r="P3" t="n">
-        <v>155.9717969674834</v>
+        <v>155.5610611184268</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -34877,37 +34877,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>53.00643562420933</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>155.141864863388</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>172.8802509475617</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>228.952183724144</v>
+        <v>4.779517641952335</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K4" t="n">
-        <v>133.058570461152</v>
+        <v>132.8490622644307</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.798404629106074</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34928,22 +34928,22 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>40.83199570698065</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>190.7613351330866</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>249.0516415124273</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -34980,28 +34980,28 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>246.9608132511783</v>
+        <v>374</v>
       </c>
       <c r="K5" t="n">
         <v>52.67130150753769</v>
       </c>
       <c r="L5" t="n">
+        <v>65.34340703517586</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>240.8741803461754</v>
+      </c>
+      <c r="P5" t="n">
         <v>374</v>
       </c>
-      <c r="M5" t="n">
+      <c r="Q5" t="n">
         <v>374</v>
-      </c>
-      <c r="N5" t="n">
-        <v>374</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>59.25677413017286</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35114,16 +35114,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>38.32672286422509</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -35138,13 +35138,13 @@
         <v>228.952183724144</v>
       </c>
       <c r="J7" t="n">
-        <v>95.17336039979469</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>133.058570461152</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>4.066502989761812</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35165,7 +35165,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>40.86342193648883</v>
       </c>
       <c r="T7" t="n">
         <v>190.7690400511193</v>
@@ -35217,10 +35217,10 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>181.6174062160024</v>
+        <v>0.1006972724976123</v>
       </c>
       <c r="K8" t="n">
-        <v>52.67130150753769</v>
+        <v>234.1880104510425</v>
       </c>
       <c r="L8" t="n">
         <v>65.34340703517591</v>
@@ -35351,13 +35351,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
         <v>119.0190951630435</v>
@@ -35375,13 +35375,13 @@
         <v>228.952183724144</v>
       </c>
       <c r="J10" t="n">
-        <v>237.0841016250218</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>133.058570461152</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>4.066502989761812</v>
+        <v>4.06650298976183</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35402,7 +35402,7 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>40.86342193648883</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -35420,7 +35420,7 @@
         <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>56.38135906334146</v>
       </c>
     </row>
     <row r="11">
@@ -35454,19 +35454,19 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>84.37734551370366</v>
+        <v>514.6820820998604</v>
       </c>
       <c r="K11" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="L11" t="n">
-        <v>222.040703517588</v>
+        <v>222.0407035175879</v>
       </c>
       <c r="M11" t="n">
-        <v>649</v>
+        <v>217.2539519487961</v>
       </c>
       <c r="N11" t="n">
-        <v>596.491643285883</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>166.8217284158573</v>
@@ -35475,7 +35475,7 @@
         <v>202.0463570447457</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>594.9733587913345</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35603,10 +35603,10 @@
         <v>46.61714403225807</v>
       </c>
       <c r="G13" t="n">
-        <v>76.58727469945357</v>
+        <v>76.58727469945359</v>
       </c>
       <c r="H13" t="n">
-        <v>97.84034930821745</v>
+        <v>97.84034930821744</v>
       </c>
       <c r="I13" t="n">
         <v>163.3468722487342</v>
@@ -35645,10 +35645,10 @@
         <v>113.6721548052177</v>
       </c>
       <c r="U13" t="n">
-        <v>158.8603714383706</v>
+        <v>170.0760349550503</v>
       </c>
       <c r="V13" t="n">
-        <v>121.8296897837838</v>
+        <v>110.6140262671042</v>
       </c>
       <c r="W13" t="n">
         <v>94.62719016129032</v>
@@ -35700,19 +35700,19 @@
         <v>222.040703517588</v>
       </c>
       <c r="M14" t="n">
-        <v>649</v>
+        <v>648.0000000000014</v>
       </c>
       <c r="N14" t="n">
-        <v>24.58449078552565</v>
+        <v>648.0000000000014</v>
       </c>
       <c r="O14" t="n">
         <v>166.8217284158573</v>
       </c>
       <c r="P14" t="n">
-        <v>649</v>
+        <v>202.0463570447457</v>
       </c>
       <c r="Q14" t="n">
-        <v>594.9733587913345</v>
+        <v>415.5518965725159</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35846,7 +35846,7 @@
         <v>97.84034930821745</v>
       </c>
       <c r="I16" t="n">
-        <v>163.3468722487342</v>
+        <v>152.1312087320547</v>
       </c>
       <c r="J16" t="n">
         <v>330.3531823116332</v>
@@ -35879,7 +35879,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>102.456491288538</v>
+        <v>113.6721548052177</v>
       </c>
       <c r="U16" t="n">
         <v>170.0760349550503</v>
@@ -35928,7 +35928,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>84.37734551370366</v>
+        <v>514.6820820998604</v>
       </c>
       <c r="K17" t="n">
         <v>178.9801507537688</v>
@@ -35937,19 +35937,19 @@
         <v>222.040703517588</v>
       </c>
       <c r="M17" t="n">
-        <v>24.58449078552576</v>
+        <v>648.0000000000014</v>
       </c>
       <c r="N17" t="n">
-        <v>649</v>
+        <v>633.2471599863601</v>
       </c>
       <c r="O17" t="n">
         <v>166.8217284158573</v>
       </c>
       <c r="P17" t="n">
-        <v>649</v>
+        <v>202.0463570447457</v>
       </c>
       <c r="Q17" t="n">
-        <v>594.9733587913345</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36071,7 +36071,7 @@
         <v>35.46378194444452</v>
       </c>
       <c r="E19" t="n">
-        <v>28.80343164636386</v>
+        <v>40.01909516304346</v>
       </c>
       <c r="F19" t="n">
         <v>46.61714403225807</v>
@@ -36116,7 +36116,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>113.6721548052177</v>
+        <v>102.4564912885381</v>
       </c>
       <c r="U19" t="n">
         <v>170.0760349550503</v>
@@ -36165,7 +36165,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>84.37734551370366</v>
+        <v>514.6820820998604</v>
       </c>
       <c r="K20" t="n">
         <v>178.9801507537688</v>
@@ -36174,10 +36174,10 @@
         <v>222.040703517588</v>
       </c>
       <c r="M20" t="n">
-        <v>649</v>
+        <v>648.0000000000014</v>
       </c>
       <c r="N20" t="n">
-        <v>471.5381337407799</v>
+        <v>38.27380119502589</v>
       </c>
       <c r="O20" t="n">
         <v>166.8217284158573</v>
@@ -36402,7 +36402,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>84.37734551370366</v>
+        <v>514.6820820998604</v>
       </c>
       <c r="K23" t="n">
         <v>178.9801507537688</v>
@@ -36411,10 +36411,10 @@
         <v>222.040703517588</v>
       </c>
       <c r="M23" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="N23" t="n">
-        <v>649</v>
+        <v>38.27380119502727</v>
       </c>
       <c r="O23" t="n">
         <v>166.8217284158573</v>
@@ -36423,7 +36423,7 @@
         <v>202.0463570447457</v>
       </c>
       <c r="Q23" t="n">
-        <v>417.5114925321143</v>
+        <v>594.9733587913345</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36560,10 +36560,10 @@
         <v>163.3468722487342</v>
       </c>
       <c r="J25" t="n">
-        <v>330.3531823116332</v>
+        <v>319.1375187949537</v>
       </c>
       <c r="K25" t="n">
-        <v>94.59143153463661</v>
+        <v>105.807095051316</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -36639,16 +36639,16 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>514.6820820998604</v>
+        <v>84.37734551370366</v>
       </c>
       <c r="K26" t="n">
         <v>178.9801507537688</v>
       </c>
       <c r="L26" t="n">
-        <v>222.040703517588</v>
+        <v>641.5117920092981</v>
       </c>
       <c r="M26" t="n">
-        <v>639.1663519055533</v>
+        <v>650</v>
       </c>
       <c r="N26" t="n">
         <v>650</v>
@@ -36785,13 +36785,13 @@
         <v>40.01909516304346</v>
       </c>
       <c r="F28" t="n">
-        <v>35.40148051557823</v>
+        <v>46.61714403225807</v>
       </c>
       <c r="G28" t="n">
-        <v>76.58727469945357</v>
+        <v>76.58727469945359</v>
       </c>
       <c r="H28" t="n">
-        <v>97.84034930821745</v>
+        <v>97.84034930821744</v>
       </c>
       <c r="I28" t="n">
         <v>163.3468722487342</v>
@@ -36827,7 +36827,7 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>113.6721548052177</v>
+        <v>102.456491288538</v>
       </c>
       <c r="U28" t="n">
         <v>170.0760349550503</v>
@@ -36876,16 +36876,16 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>514.6820820998604</v>
+        <v>84.37734551370366</v>
       </c>
       <c r="K29" t="n">
         <v>178.9801507537688</v>
       </c>
       <c r="L29" t="n">
-        <v>222.040703517588</v>
+        <v>641.5117920092981</v>
       </c>
       <c r="M29" t="n">
-        <v>639.1663519055533</v>
+        <v>650</v>
       </c>
       <c r="N29" t="n">
         <v>650</v>
@@ -37013,22 +37013,22 @@
         <v>33.88619966292134</v>
       </c>
       <c r="C31" t="n">
-        <v>37.05908983527552</v>
+        <v>48.27475335195533</v>
       </c>
       <c r="D31" t="n">
         <v>35.46378194444452</v>
       </c>
       <c r="E31" t="n">
-        <v>40.01909516304346</v>
+        <v>28.80343164636363</v>
       </c>
       <c r="F31" t="n">
         <v>46.61714403225807</v>
       </c>
       <c r="G31" t="n">
-        <v>76.58727469945359</v>
+        <v>76.58727469945357</v>
       </c>
       <c r="H31" t="n">
-        <v>97.84034930821744</v>
+        <v>97.84034930821745</v>
       </c>
       <c r="I31" t="n">
         <v>163.3468722487342</v>
@@ -37113,7 +37113,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>514.6820820998604</v>
+        <v>84.37734551370366</v>
       </c>
       <c r="K32" t="n">
         <v>178.9801507537688</v>
@@ -37122,19 +37122,19 @@
         <v>222.040703517588</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>474.4977297003759</v>
       </c>
       <c r="N32" t="n">
         <v>650</v>
       </c>
       <c r="O32" t="n">
-        <v>358.0344373661565</v>
+        <v>166.8217284158573</v>
       </c>
       <c r="P32" t="n">
-        <v>650</v>
+        <v>202.0463570447457</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>594.9733587913345</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37259,19 +37259,19 @@
         <v>40.01909516304346</v>
       </c>
       <c r="F34" t="n">
-        <v>35.40148051557823</v>
+        <v>46.61714403225807</v>
       </c>
       <c r="G34" t="n">
-        <v>76.58727469945357</v>
+        <v>76.58727469945359</v>
       </c>
       <c r="H34" t="n">
-        <v>97.84034930821745</v>
+        <v>97.84034930821744</v>
       </c>
       <c r="I34" t="n">
         <v>163.3468722487342</v>
       </c>
       <c r="J34" t="n">
-        <v>330.3531823116332</v>
+        <v>319.1375187949535</v>
       </c>
       <c r="K34" t="n">
         <v>105.807095051316</v>
@@ -37350,7 +37350,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>514.6820820998604</v>
+        <v>84.37734551370366</v>
       </c>
       <c r="K35" t="n">
         <v>178.9801507537688</v>
@@ -37359,10 +37359,10 @@
         <v>222.040703517588</v>
       </c>
       <c r="M35" t="n">
-        <v>559.0000000000089</v>
+        <v>564</v>
       </c>
       <c r="N35" t="n">
-        <v>369.8431195823123</v>
+        <v>564</v>
       </c>
       <c r="O35" t="n">
         <v>166.8217284158573</v>
@@ -37371,7 +37371,7 @@
         <v>202.0463570447457</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>250.9458359664578</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37438,7 +37438,7 @@
         <v>437.5512810090644</v>
       </c>
       <c r="M36" t="n">
-        <v>258.4357286609326</v>
+        <v>277.7000421645042</v>
       </c>
       <c r="N36" t="n">
         <v>330.4251350143152</v>
@@ -37484,37 +37484,37 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>57.88619966292134</v>
+        <v>56.88619966292134</v>
       </c>
       <c r="C37" t="n">
-        <v>72.27475335195533</v>
+        <v>71.27475335195533</v>
       </c>
       <c r="D37" t="n">
-        <v>59.46378194444452</v>
+        <v>58.46378194444452</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>63.01909516304346</v>
       </c>
       <c r="F37" t="n">
-        <v>70.61714403225807</v>
+        <v>69.61714403225807</v>
       </c>
       <c r="G37" t="n">
-        <v>89.87027460158873</v>
+        <v>99.58727469945359</v>
       </c>
       <c r="H37" t="n">
-        <v>121.8403493082175</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>187.3468722487342</v>
+        <v>186.3468722487342</v>
       </c>
       <c r="J37" t="n">
-        <v>354.3531823116332</v>
+        <v>9.353182311633219</v>
       </c>
       <c r="K37" t="n">
-        <v>129.807095051316</v>
+        <v>128.807095051316</v>
       </c>
       <c r="L37" t="n">
-        <v>15.28679807172902</v>
+        <v>14.28679807172904</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -37538,22 +37538,22 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>137.6721548052177</v>
+        <v>136.6721548052177</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>193.0760349550503</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>43.00851013468028</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>117.6271901612903</v>
       </c>
       <c r="X37" t="n">
-        <v>97.55635456989245</v>
+        <v>96.55635456989245</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>56.53464715053764</v>
       </c>
     </row>
     <row r="38">
@@ -37587,19 +37587,19 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>514.6820820998604</v>
+        <v>84.37734551370366</v>
       </c>
       <c r="K38" t="n">
-        <v>559</v>
+        <v>178.9801507537688</v>
       </c>
       <c r="L38" t="n">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="M38" t="n">
-        <v>211.8639738536781</v>
+        <v>472.9865394840459</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>564</v>
       </c>
       <c r="O38" t="n">
         <v>166.8217284158573</v>
@@ -37675,7 +37675,7 @@
         <v>437.5512810090644</v>
       </c>
       <c r="M39" t="n">
-        <v>258.4357286609326</v>
+        <v>277.7000421645042</v>
       </c>
       <c r="N39" t="n">
         <v>330.4251350143152</v>
@@ -37721,37 +37721,37 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>57.88619966292134</v>
+        <v>56.88619966292134</v>
       </c>
       <c r="C40" t="n">
-        <v>72.27475335195533</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>59.46378194444452</v>
+        <v>58.46378194444452</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>63.01909516304346</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>69.61714403225807</v>
       </c>
       <c r="G40" t="n">
-        <v>100.5872746994536</v>
+        <v>99.58727469945357</v>
       </c>
       <c r="H40" t="n">
-        <v>121.8403493082175</v>
+        <v>120.8403493082175</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>354.3531823116332</v>
+        <v>353.3531823116332</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>115.5558343554152</v>
       </c>
       <c r="L40" t="n">
-        <v>15.28679807172902</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -37775,22 +37775,22 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>137.6721548052177</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>194.0760349550503</v>
+        <v>193.0760349550503</v>
       </c>
       <c r="V40" t="n">
-        <v>6.816238967565258</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>118.6271901612903</v>
+        <v>117.6271901612903</v>
       </c>
       <c r="X40" t="n">
-        <v>97.55635456989245</v>
+        <v>96.55635456989245</v>
       </c>
       <c r="Y40" t="n">
-        <v>57.53464715053764</v>
+        <v>56.53464715053764</v>
       </c>
     </row>
     <row r="41">
@@ -37833,10 +37833,10 @@
         <v>222.040703517588</v>
       </c>
       <c r="M41" t="n">
-        <v>241.147856168402</v>
+        <v>564</v>
       </c>
       <c r="N41" t="n">
-        <v>559.000000000038</v>
+        <v>564</v>
       </c>
       <c r="O41" t="n">
         <v>166.8217284158573</v>
@@ -37845,7 +37845,7 @@
         <v>202.0463570447457</v>
       </c>
       <c r="Q41" t="n">
-        <v>559.000000000038</v>
+        <v>250.9458359664578</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37909,7 +37909,7 @@
         <v>312.6694206785272</v>
       </c>
       <c r="L42" t="n">
-        <v>418.2869675054928</v>
+        <v>437.5512810090644</v>
       </c>
       <c r="M42" t="n">
         <v>277.7000421645042</v>
@@ -37973,10 +37973,10 @@
         <v>46.61714403225807</v>
       </c>
       <c r="G43" t="n">
-        <v>76.58727469945357</v>
+        <v>76.58727469945359</v>
       </c>
       <c r="H43" t="n">
-        <v>97.84034930821745</v>
+        <v>97.84034930821744</v>
       </c>
       <c r="I43" t="n">
         <v>163.3468722487342</v>
@@ -38012,10 +38012,10 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>102.4564912885382</v>
+        <v>113.6721548052177</v>
       </c>
       <c r="U43" t="n">
-        <v>170.0760349550503</v>
+        <v>158.8603714383706</v>
       </c>
       <c r="V43" t="n">
         <v>121.8296897837838</v>
@@ -38070,10 +38070,10 @@
         <v>222.040703517588</v>
       </c>
       <c r="M44" t="n">
-        <v>559.0000000000671</v>
+        <v>564</v>
       </c>
       <c r="N44" t="n">
-        <v>559.0000000000671</v>
+        <v>250.9458359664576</v>
       </c>
       <c r="O44" t="n">
         <v>166.8217284158573</v>
@@ -38082,7 +38082,7 @@
         <v>202.0463570447457</v>
       </c>
       <c r="Q44" t="n">
-        <v>241.1478561686234</v>
+        <v>564</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38155,7 +38155,7 @@
         <v>330.4251350143152</v>
       </c>
       <c r="O45" t="n">
-        <v>401.310161229643</v>
+        <v>420.5744747329351</v>
       </c>
       <c r="P45" t="n">
         <v>257.4235516844645</v>
@@ -38222,7 +38222,7 @@
         <v>330.3531823116332</v>
       </c>
       <c r="K46" t="n">
-        <v>105.807095051316</v>
+        <v>94.59143153463638</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -38249,7 +38249,7 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>102.4564912885382</v>
+        <v>113.6721548052177</v>
       </c>
       <c r="U46" t="n">
         <v>170.0760349550503</v>
